--- a/reports/_comparative_4_scenarios/comparative_report_4_scenarios.xlsx
+++ b/reports/_comparative_4_scenarios/comparative_report_4_scenarios.xlsx
@@ -14151,7 +14151,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -14184,37 +14184,37 @@
         </is>
       </c>
       <c r="J146" t="n">
-        <v>7.919425487518311</v>
+        <v>60.36861348152161</v>
       </c>
       <c r="K146" t="n">
-        <v>0.8963520100241514</v>
+        <v>0.8861158550177131</v>
       </c>
       <c r="L146" t="n">
-        <v>0.8660765626746049</v>
+        <v>0.8829669114684049</v>
       </c>
       <c r="M146" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="N146" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="O146" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="P146" t="n">
-        <v>1.11392816382589</v>
+        <v>3.577812784336889</v>
       </c>
       <c r="Q146" t="n">
-        <v>3.331245740935037</v>
+        <v>62.19613654096213</v>
       </c>
       <c r="R146" t="n">
-        <v>0.2981121217024075</v>
+        <v>0.1976667855385119</v>
       </c>
       <c r="S146" t="n">
-        <v>4.743286026463334</v>
+        <v>65.97161611083753</v>
       </c>
       <c r="T146" t="n">
-        <v>210.824309228009</v>
+        <v>15.15803399934786</v>
       </c>
       <c r="U146" t="inlineStr">
         <is>
@@ -14248,7 +14248,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -14281,37 +14281,37 @@
         </is>
       </c>
       <c r="J147" t="n">
-        <v>9.623297214508057</v>
+        <v>60.18165683746338</v>
       </c>
       <c r="K147" t="n">
-        <v>0.8963520100241514</v>
+        <v>0.8861158550177131</v>
       </c>
       <c r="L147" t="n">
-        <v>0.8660765626746049</v>
+        <v>0.8829669114684049</v>
       </c>
       <c r="M147" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="N147" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="O147" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="P147" t="n">
-        <v>1.253191286763555</v>
+        <v>3.389318269883992</v>
       </c>
       <c r="Q147" t="n">
-        <v>4.189332919293476</v>
+        <v>62.37194781927823</v>
       </c>
       <c r="R147" t="n">
-        <v>0.3370381445877804</v>
+        <v>0.1931943999960526</v>
       </c>
       <c r="S147" t="n">
-        <v>5.779562350644812</v>
+        <v>65.95446048915828</v>
       </c>
       <c r="T147" t="n">
-        <v>173.023481594317</v>
+        <v>15.16197680313649</v>
       </c>
       <c r="U147" t="inlineStr">
         <is>
@@ -14345,7 +14345,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -14378,37 +14378,37 @@
         </is>
       </c>
       <c r="J148" t="n">
-        <v>8.807447671890259</v>
+        <v>61.96895003318787</v>
       </c>
       <c r="K148" t="n">
-        <v>0.8963520100241514</v>
+        <v>0.8861158550177131</v>
       </c>
       <c r="L148" t="n">
-        <v>0.8660765626746049</v>
+        <v>0.8829669114684049</v>
       </c>
       <c r="M148" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="N148" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="O148" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="P148" t="n">
-        <v>1.218224668658636</v>
+        <v>3.411678866263152</v>
       </c>
       <c r="Q148" t="n">
-        <v>3.698993178317411</v>
+        <v>63.74046757107902</v>
       </c>
       <c r="R148" t="n">
-        <v>0.3291073975779877</v>
+        <v>0.1977146614480952</v>
       </c>
       <c r="S148" t="n">
-        <v>5.246325244554034</v>
+        <v>67.34986109879026</v>
       </c>
       <c r="T148" t="n">
-        <v>190.6096083230931</v>
+        <v>14.84784056990374</v>
       </c>
       <c r="U148" t="inlineStr">
         <is>
@@ -14442,7 +14442,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -14475,37 +14475,37 @@
         </is>
       </c>
       <c r="J149" t="n">
-        <v>9.109304189682009</v>
+        <v>61.25183415412903</v>
       </c>
       <c r="K149" t="n">
-        <v>0.8526107293020055</v>
+        <v>0.8554559725472815</v>
       </c>
       <c r="L149" t="n">
-        <v>0.8344556377524764</v>
+        <v>0.8466160774728351</v>
       </c>
       <c r="M149" t="n">
-        <v>0.8972129987083401</v>
+        <v>0.9138390369805568</v>
       </c>
       <c r="N149" t="n">
-        <v>0.7578056823174325</v>
+        <v>0.7792668464347121</v>
       </c>
       <c r="O149" t="n">
-        <v>0.7578056823174325</v>
+        <v>0.7792668464347121</v>
       </c>
       <c r="P149" t="n">
-        <v>1.178099043370668</v>
+        <v>2.823422363845917</v>
       </c>
       <c r="Q149" t="n">
-        <v>3.615107284318824</v>
+        <v>61.99228953855325</v>
       </c>
       <c r="R149" t="n">
-        <v>0.3302919927525828</v>
+        <v>0.1924064445750237</v>
       </c>
       <c r="S149" t="n">
-        <v>5.123498320442075</v>
+        <v>65.0081183469742</v>
       </c>
       <c r="T149" t="n">
-        <v>195.1791407855319</v>
+        <v>15.38269412233411</v>
       </c>
       <c r="U149" t="inlineStr">
         <is>
@@ -14539,7 +14539,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -14572,37 +14572,37 @@
         </is>
       </c>
       <c r="J150" t="n">
-        <v>9.767948627471924</v>
+        <v>60.29372668266296</v>
       </c>
       <c r="K150" t="n">
-        <v>0.8526107293020055</v>
+        <v>0.8554559725472815</v>
       </c>
       <c r="L150" t="n">
-        <v>0.8344556377524764</v>
+        <v>0.8466160774728351</v>
       </c>
       <c r="M150" t="n">
-        <v>0.8972129987083401</v>
+        <v>0.9138390369805568</v>
       </c>
       <c r="N150" t="n">
-        <v>0.7578056823174325</v>
+        <v>0.7792668464347121</v>
       </c>
       <c r="O150" t="n">
-        <v>0.7578056823174325</v>
+        <v>0.7792668464347121</v>
       </c>
       <c r="P150" t="n">
-        <v>1.251274537317369</v>
+        <v>3.255934819278454</v>
       </c>
       <c r="Q150" t="n">
-        <v>4.304716331348737</v>
+        <v>62.35827147952231</v>
       </c>
       <c r="R150" t="n">
-        <v>0.3350898818755823</v>
+        <v>0.1926298638485911</v>
       </c>
       <c r="S150" t="n">
-        <v>5.891080750541688</v>
+        <v>65.80683616264936</v>
       </c>
       <c r="T150" t="n">
-        <v>169.7481400009751</v>
+        <v>15.19598963135657</v>
       </c>
       <c r="U150" t="inlineStr">
         <is>
@@ -14636,7 +14636,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -14669,37 +14669,37 @@
         </is>
       </c>
       <c r="J151" t="n">
-        <v>8.508018255233765</v>
+        <v>61.55682325363159</v>
       </c>
       <c r="K151" t="n">
-        <v>0.8526107293020055</v>
+        <v>0.8554559725472815</v>
       </c>
       <c r="L151" t="n">
-        <v>0.8344556377524764</v>
+        <v>0.8466160774728351</v>
       </c>
       <c r="M151" t="n">
-        <v>0.8972129987083401</v>
+        <v>0.9138390369805568</v>
       </c>
       <c r="N151" t="n">
-        <v>0.7578056823174325</v>
+        <v>0.7792668464347121</v>
       </c>
       <c r="O151" t="n">
-        <v>0.7578056823174325</v>
+        <v>0.7792668464347121</v>
       </c>
       <c r="P151" t="n">
-        <v>1.166719560232118</v>
+        <v>3.363454225299152</v>
       </c>
       <c r="Q151" t="n">
-        <v>3.455434873495801</v>
+        <v>63.5377552445712</v>
       </c>
       <c r="R151" t="n">
-        <v>0.3199979036417719</v>
+        <v>0.1923058012109147</v>
       </c>
       <c r="S151" t="n">
-        <v>4.942152337369691</v>
+        <v>67.09351527108127</v>
       </c>
       <c r="T151" t="n">
-        <v>202.3409906729462</v>
+        <v>14.90457007595518</v>
       </c>
       <c r="U151" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -14766,37 +14766,37 @@
         </is>
       </c>
       <c r="J152" t="n">
-        <v>9.51214861869812</v>
+        <v>62.94834685325623</v>
       </c>
       <c r="K152" t="n">
-        <v>0.725789278693295</v>
+        <v>0.7588249804831326</v>
       </c>
       <c r="L152" t="n">
-        <v>0.7286047915157121</v>
+        <v>0.7149502064942947</v>
       </c>
       <c r="M152" t="n">
-        <v>0.7707737698172715</v>
+        <v>0.7787717652837904</v>
       </c>
       <c r="N152" t="n">
-        <v>0.6240064954710411</v>
+        <v>0.6254110464216518</v>
       </c>
       <c r="O152" t="n">
-        <v>0.6240064954710411</v>
+        <v>0.6254110464216518</v>
       </c>
       <c r="P152" t="n">
-        <v>1.261353527777565</v>
+        <v>3.201961490365548</v>
       </c>
       <c r="Q152" t="n">
-        <v>4.083493655442393</v>
+        <v>63.81637453132169</v>
       </c>
       <c r="R152" t="n">
-        <v>0.3286296807499342</v>
+        <v>0.194701428919476</v>
       </c>
       <c r="S152" t="n">
-        <v>5.673476863969892</v>
+        <v>67.21303745060672</v>
       </c>
       <c r="T152" t="n">
-        <v>176.258760540758</v>
+        <v>14.87806589212512</v>
       </c>
       <c r="U152" t="inlineStr">
         <is>
@@ -14830,7 +14830,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -14863,37 +14863,37 @@
         </is>
       </c>
       <c r="J153" t="n">
-        <v>9.743237733840942</v>
+        <v>61.92353343963623</v>
       </c>
       <c r="K153" t="n">
-        <v>0.725789278693295</v>
+        <v>0.7588249804831326</v>
       </c>
       <c r="L153" t="n">
-        <v>0.7286047915157121</v>
+        <v>0.7149502064942947</v>
       </c>
       <c r="M153" t="n">
-        <v>0.7707737698172715</v>
+        <v>0.7787717652837904</v>
       </c>
       <c r="N153" t="n">
-        <v>0.6240064954710411</v>
+        <v>0.6254110464216518</v>
       </c>
       <c r="O153" t="n">
-        <v>0.6240064954710411</v>
+        <v>0.6254110464216518</v>
       </c>
       <c r="P153" t="n">
-        <v>1.303999057811133</v>
+        <v>3.082908084335546</v>
       </c>
       <c r="Q153" t="n">
-        <v>4.277113281921585</v>
+        <v>63.68552276024423</v>
       </c>
       <c r="R153" t="n">
-        <v>0.3562860180787232</v>
+        <v>0.1913050385621361</v>
       </c>
       <c r="S153" t="n">
-        <v>5.937398357811441</v>
+        <v>66.9597358831419</v>
       </c>
       <c r="T153" t="n">
-        <v>168.4239358277799</v>
+        <v>14.9343480348429</v>
       </c>
       <c r="U153" t="inlineStr">
         <is>
@@ -14927,7 +14927,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -14960,37 +14960,37 @@
         </is>
       </c>
       <c r="J154" t="n">
-        <v>8.069807767868042</v>
+        <v>64.00447082519531</v>
       </c>
       <c r="K154" t="n">
-        <v>0.725789278693295</v>
+        <v>0.7588249804831326</v>
       </c>
       <c r="L154" t="n">
-        <v>0.7286047915157121</v>
+        <v>0.7149502064942947</v>
       </c>
       <c r="M154" t="n">
-        <v>0.7707737698172715</v>
+        <v>0.7787717652837904</v>
       </c>
       <c r="N154" t="n">
-        <v>0.6240064954710411</v>
+        <v>0.6254110464216518</v>
       </c>
       <c r="O154" t="n">
-        <v>0.6240064954710411</v>
+        <v>0.6254110464216518</v>
       </c>
       <c r="P154" t="n">
-        <v>1.167614981910359</v>
+        <v>3.42083200120576</v>
       </c>
       <c r="Q154" t="n">
-        <v>3.40827184698421</v>
+        <v>66.0140007686731</v>
       </c>
       <c r="R154" t="n">
-        <v>0.3071769952105361</v>
+        <v>0.201378977107449</v>
       </c>
       <c r="S154" t="n">
-        <v>4.883063824105106</v>
+        <v>69.63621174698631</v>
       </c>
       <c r="T154" t="n">
-        <v>204.7894592455516</v>
+        <v>14.36034463840974</v>
       </c>
       <c r="U154" t="inlineStr">
         <is>
@@ -15024,7 +15024,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -15057,37 +15057,37 @@
         </is>
       </c>
       <c r="J155" t="n">
-        <v>9.740017175674438</v>
+        <v>63.34791970252991</v>
       </c>
       <c r="K155" t="n">
-        <v>0.6807838867983227</v>
+        <v>0.6299930781790891</v>
       </c>
       <c r="L155" t="n">
-        <v>0.4938162375024422</v>
+        <v>0.5236990023280943</v>
       </c>
       <c r="M155" t="n">
-        <v>0.5214984470712496</v>
+        <v>0.5807748643741676</v>
       </c>
       <c r="N155" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="O155" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="P155" t="n">
-        <v>1.246810051796559</v>
+        <v>3.114497473501593</v>
       </c>
       <c r="Q155" t="n">
-        <v>4.223361703643824</v>
+        <v>64.71123215180988</v>
       </c>
       <c r="R155" t="n">
-        <v>0.3660892397540492</v>
+        <v>0.1901969301299511</v>
       </c>
       <c r="S155" t="n">
-        <v>5.836260995194432</v>
+        <v>68.01592655544142</v>
       </c>
       <c r="T155" t="n">
-        <v>171.3425771779909</v>
+        <v>14.70243883518775</v>
       </c>
       <c r="U155" t="inlineStr">
         <is>
@@ -15121,7 +15121,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -15154,37 +15154,37 @@
         </is>
       </c>
       <c r="J156" t="n">
-        <v>9.596434593200684</v>
+        <v>58.4327507019043</v>
       </c>
       <c r="K156" t="n">
-        <v>0.6807838867983227</v>
+        <v>0.6299930781790891</v>
       </c>
       <c r="L156" t="n">
-        <v>0.4938162375024422</v>
+        <v>0.5236990023280943</v>
       </c>
       <c r="M156" t="n">
-        <v>0.5214984470712496</v>
+        <v>0.5807748643741676</v>
       </c>
       <c r="N156" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="O156" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="P156" t="n">
-        <v>1.260260268671951</v>
+        <v>3.072257202399329</v>
       </c>
       <c r="Q156" t="n">
-        <v>4.050318887940708</v>
+        <v>60.14954761686918</v>
       </c>
       <c r="R156" t="n">
-        <v>0.3390045204611512</v>
+        <v>0.1889928795246459</v>
       </c>
       <c r="S156" t="n">
-        <v>5.649583677073811</v>
+        <v>63.41079769879315</v>
       </c>
       <c r="T156" t="n">
-        <v>177.0041930802851</v>
+        <v>15.77018483114008</v>
       </c>
       <c r="U156" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -15251,37 +15251,37 @@
         </is>
       </c>
       <c r="J157" t="n">
-        <v>9.07709002494812</v>
+        <v>58.60601186752319</v>
       </c>
       <c r="K157" t="n">
-        <v>0.6807838867983227</v>
+        <v>0.6299930781790891</v>
       </c>
       <c r="L157" t="n">
-        <v>0.4938162375024422</v>
+        <v>0.5236990023280943</v>
       </c>
       <c r="M157" t="n">
-        <v>0.5214984470712496</v>
+        <v>0.5807748643741676</v>
       </c>
       <c r="N157" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="O157" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="P157" t="n">
-        <v>1.215600822889614</v>
+        <v>3.035289937345197</v>
       </c>
       <c r="Q157" t="n">
-        <v>3.836754749436405</v>
+        <v>60.19008606988199</v>
       </c>
       <c r="R157" t="n">
-        <v>0.3256693349744253</v>
+        <v>0.1863357096445692</v>
       </c>
       <c r="S157" t="n">
-        <v>5.378024907300444</v>
+        <v>63.41171171687176</v>
       </c>
       <c r="T157" t="n">
-        <v>185.941868480851</v>
+        <v>15.76995751928162</v>
       </c>
       <c r="U157" t="inlineStr">
         <is>
@@ -15315,7 +15315,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -15348,37 +15348,37 @@
         </is>
       </c>
       <c r="J158" t="n">
-        <v>10.14369201660156</v>
+        <v>59.18736863136292</v>
       </c>
       <c r="K158" t="n">
-        <v>0.9111316364542188</v>
+        <v>0.9165630081374349</v>
       </c>
       <c r="L158" t="n">
-        <v>0.8496529487895471</v>
+        <v>0.8429371880628344</v>
       </c>
       <c r="M158" t="n">
-        <v>0.9183375572963552</v>
+        <v>0.9190307552534428</v>
       </c>
       <c r="N158" t="n">
-        <v>0.7868302589310699</v>
+        <v>0.7960427176781357</v>
       </c>
       <c r="O158" t="n">
-        <v>0.7868302589310699</v>
+        <v>0.7960427176781357</v>
       </c>
       <c r="P158" t="n">
-        <v>1.267715632577647</v>
+        <v>2.939649191577416</v>
       </c>
       <c r="Q158" t="n">
-        <v>4.43443337350022</v>
+        <v>59.31122958553966</v>
       </c>
       <c r="R158" t="n">
-        <v>0.3671151903871354</v>
+        <v>0.1898501807219478</v>
       </c>
       <c r="S158" t="n">
-        <v>6.069264196465003</v>
+        <v>62.44072895783903</v>
       </c>
       <c r="T158" t="n">
-        <v>164.7646185154442</v>
+        <v>16.01518778993141</v>
       </c>
       <c r="U158" t="inlineStr">
         <is>
@@ -15412,7 +15412,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -15445,37 +15445,37 @@
         </is>
       </c>
       <c r="J159" t="n">
-        <v>8.955272197723389</v>
+        <v>58.07856726646423</v>
       </c>
       <c r="K159" t="n">
-        <v>0.9111316364542188</v>
+        <v>0.9165630081374349</v>
       </c>
       <c r="L159" t="n">
-        <v>0.8496529487895471</v>
+        <v>0.8429371880628344</v>
       </c>
       <c r="M159" t="n">
-        <v>0.9183375572963552</v>
+        <v>0.9190307552534428</v>
       </c>
       <c r="N159" t="n">
-        <v>0.7868302589310699</v>
+        <v>0.7960427176781357</v>
       </c>
       <c r="O159" t="n">
-        <v>0.7868302589310699</v>
+        <v>0.7960427176781357</v>
       </c>
       <c r="P159" t="n">
-        <v>1.194461401231031</v>
+        <v>3.254788601205576</v>
       </c>
       <c r="Q159" t="n">
-        <v>3.783325237326422</v>
+        <v>59.18442078434263</v>
       </c>
       <c r="R159" t="n">
-        <v>0.3344970337700461</v>
+        <v>0.1847110012005876</v>
       </c>
       <c r="S159" t="n">
-        <v>5.312283672327498</v>
+        <v>62.62392038674879</v>
       </c>
       <c r="T159" t="n">
-        <v>188.2429594656539</v>
+        <v>15.96833915577728</v>
       </c>
       <c r="U159" t="inlineStr">
         <is>
@@ -15509,7 +15509,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -15542,37 +15542,37 @@
         </is>
       </c>
       <c r="J160" t="n">
-        <v>9.618680715560911</v>
+        <v>58.37568521499634</v>
       </c>
       <c r="K160" t="n">
-        <v>0.9111316364542188</v>
+        <v>0.9165630081374349</v>
       </c>
       <c r="L160" t="n">
-        <v>0.8496529487895471</v>
+        <v>0.8429371880628344</v>
       </c>
       <c r="M160" t="n">
-        <v>0.9183375572963552</v>
+        <v>0.9190307552534428</v>
       </c>
       <c r="N160" t="n">
-        <v>0.7868302589310699</v>
+        <v>0.7960427176781357</v>
       </c>
       <c r="O160" t="n">
-        <v>0.7868302589310699</v>
+        <v>0.7960427176781357</v>
       </c>
       <c r="P160" t="n">
-        <v>1.239635516876332</v>
+        <v>3.179339691577439</v>
       </c>
       <c r="Q160" t="n">
-        <v>4.153844390382429</v>
+        <v>59.45247530481505</v>
       </c>
       <c r="R160" t="n">
-        <v>0.3299652867877213</v>
+        <v>0.1850417975926674</v>
       </c>
       <c r="S160" t="n">
-        <v>5.723445194046482</v>
+        <v>62.81685679398516</v>
       </c>
       <c r="T160" t="n">
-        <v>174.7199398432605</v>
+        <v>15.91929381757528</v>
       </c>
       <c r="U160" t="inlineStr">
         <is>
@@ -15606,7 +15606,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -15639,37 +15639,37 @@
         </is>
       </c>
       <c r="J161" t="n">
-        <v>10.05600571632385</v>
+        <v>58.54555773735046</v>
       </c>
       <c r="K161" t="n">
-        <v>0.8851604328572649</v>
+        <v>0.8017734960824066</v>
       </c>
       <c r="L161" t="n">
-        <v>0.8277690110699493</v>
+        <v>0.8940013709838216</v>
       </c>
       <c r="M161" t="n">
-        <v>0.8903329101751702</v>
+        <v>0.9007055798541789</v>
       </c>
       <c r="N161" t="n">
-        <v>0.7480057530889146</v>
+        <v>0.7730690891765476</v>
       </c>
       <c r="O161" t="n">
-        <v>0.7480057530889146</v>
+        <v>0.7730690891765476</v>
       </c>
       <c r="P161" t="n">
-        <v>1.312469904804452</v>
+        <v>2.257072510839687</v>
       </c>
       <c r="Q161" t="n">
-        <v>4.492682968621779</v>
+        <v>59.76109326506629</v>
       </c>
       <c r="R161" t="n">
-        <v>0.3570374590423623</v>
+        <v>0.1917534168728433</v>
       </c>
       <c r="S161" t="n">
-        <v>6.162190332468593</v>
+        <v>62.20991919277882</v>
       </c>
       <c r="T161" t="n">
-        <v>162.2799598920205</v>
+        <v>16.07460695940074</v>
       </c>
       <c r="U161" t="inlineStr">
         <is>
@@ -15703,7 +15703,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -15736,37 +15736,37 @@
         </is>
       </c>
       <c r="J162" t="n">
-        <v>8.084418058395386</v>
+        <v>60.11703562736511</v>
       </c>
       <c r="K162" t="n">
-        <v>0.8851604328572649</v>
+        <v>0.8017734960824066</v>
       </c>
       <c r="L162" t="n">
-        <v>0.8277690110699493</v>
+        <v>0.8940013709838216</v>
       </c>
       <c r="M162" t="n">
-        <v>0.8903329101751702</v>
+        <v>0.9007055798541789</v>
       </c>
       <c r="N162" t="n">
-        <v>0.7480057530889146</v>
+        <v>0.7730690891765476</v>
       </c>
       <c r="O162" t="n">
-        <v>0.7480057530889146</v>
+        <v>0.7730690891765476</v>
       </c>
       <c r="P162" t="n">
-        <v>1.174304463906499</v>
+        <v>3.185337322891274</v>
       </c>
       <c r="Q162" t="n">
-        <v>3.402678697609398</v>
+        <v>61.61327758193101</v>
       </c>
       <c r="R162" t="n">
-        <v>0.3022753277540884</v>
+        <v>0.1924727746920478</v>
       </c>
       <c r="S162" t="n">
-        <v>4.879258489269986</v>
+        <v>64.99108767951434</v>
       </c>
       <c r="T162" t="n">
-        <v>204.9491745926369</v>
+        <v>15.38672509885086</v>
       </c>
       <c r="U162" t="inlineStr">
         <is>
@@ -15800,7 +15800,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -15833,37 +15833,37 @@
         </is>
       </c>
       <c r="J163" t="n">
-        <v>9.823601245880129</v>
+        <v>59.21114325523376</v>
       </c>
       <c r="K163" t="n">
-        <v>0.8851604328572649</v>
+        <v>0.8017734960824066</v>
       </c>
       <c r="L163" t="n">
-        <v>0.8277690110699493</v>
+        <v>0.8940013709838216</v>
       </c>
       <c r="M163" t="n">
-        <v>0.8903329101751702</v>
+        <v>0.9007055798541789</v>
       </c>
       <c r="N163" t="n">
-        <v>0.7480057530889146</v>
+        <v>0.7730690891765476</v>
       </c>
       <c r="O163" t="n">
-        <v>0.7480057530889146</v>
+        <v>0.7730690891765476</v>
       </c>
       <c r="P163" t="n">
-        <v>1.272385986694973</v>
+        <v>3.215766483129531</v>
       </c>
       <c r="Q163" t="n">
-        <v>4.331263360222966</v>
+        <v>61.09331517349489</v>
       </c>
       <c r="R163" t="n">
-        <v>0.3429453711004202</v>
+        <v>0.1928231807224039</v>
       </c>
       <c r="S163" t="n">
-        <v>5.946594718018359</v>
+        <v>64.50190483734681</v>
       </c>
       <c r="T163" t="n">
-        <v>168.1634695853697</v>
+        <v>15.50341811643672</v>
       </c>
       <c r="U163" t="inlineStr">
         <is>
@@ -15897,7 +15897,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -15930,37 +15930,37 @@
         </is>
       </c>
       <c r="J164" t="n">
-        <v>9.939846038818359</v>
+        <v>59.42232847213745</v>
       </c>
       <c r="K164" t="n">
-        <v>0.9045575585741988</v>
+        <v>0.8297052480181289</v>
       </c>
       <c r="L164" t="n">
-        <v>0.7456976377342096</v>
+        <v>0.8295355941953315</v>
       </c>
       <c r="M164" t="n">
-        <v>0.8870791824205587</v>
+        <v>0.8832205855459414</v>
       </c>
       <c r="N164" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="O164" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="P164" t="n">
-        <v>1.287515624090998</v>
+        <v>3.03285987229119</v>
       </c>
       <c r="Q164" t="n">
-        <v>4.268527997595241</v>
+        <v>60.37858796024515</v>
       </c>
       <c r="R164" t="n">
-        <v>0.3333776963875399</v>
+        <v>0.1890228277206696</v>
       </c>
       <c r="S164" t="n">
-        <v>5.889421318073778</v>
+        <v>63.60047066025701</v>
       </c>
       <c r="T164" t="n">
-        <v>169.7959690761375</v>
+        <v>15.72315408390343</v>
       </c>
       <c r="U164" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -16027,37 +16027,37 @@
         </is>
       </c>
       <c r="J165" t="n">
-        <v>8.348035335540771</v>
+        <v>56.87005281448364</v>
       </c>
       <c r="K165" t="n">
-        <v>0.9045575585741988</v>
+        <v>0.8297052480181289</v>
       </c>
       <c r="L165" t="n">
-        <v>0.7456976377342096</v>
+        <v>0.8295355941953315</v>
       </c>
       <c r="M165" t="n">
-        <v>0.8870791824205587</v>
+        <v>0.8832205855459414</v>
       </c>
       <c r="N165" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="O165" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="P165" t="n">
-        <v>1.159636200062811</v>
+        <v>1.717446163850702</v>
       </c>
       <c r="Q165" t="n">
-        <v>3.487645795207919</v>
+        <v>60.31156338191199</v>
       </c>
       <c r="R165" t="n">
-        <v>0.3064756710736252</v>
+        <v>0.1693475192803225</v>
       </c>
       <c r="S165" t="n">
-        <v>4.953757666344354</v>
+        <v>62.19835706504301</v>
       </c>
       <c r="T165" t="n">
-        <v>201.8669598624016</v>
+        <v>16.07759508750793</v>
       </c>
       <c r="U165" t="inlineStr">
         <is>
@@ -16091,7 +16091,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -16124,37 +16124,37 @@
         </is>
       </c>
       <c r="J166" t="n">
-        <v>10.04682850837708</v>
+        <v>58.58240652084351</v>
       </c>
       <c r="K166" t="n">
-        <v>0.9045575585741988</v>
+        <v>0.8297052480181289</v>
       </c>
       <c r="L166" t="n">
-        <v>0.7456976377342096</v>
+        <v>0.8295355941953315</v>
       </c>
       <c r="M166" t="n">
-        <v>0.8870791824205587</v>
+        <v>0.8832205855459414</v>
       </c>
       <c r="N166" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="O166" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="P166" t="n">
-        <v>1.322087873500479</v>
+        <v>1.761506943363333</v>
       </c>
       <c r="Q166" t="n">
-        <v>4.354311033686432</v>
+        <v>62.04982790481406</v>
       </c>
       <c r="R166" t="n">
-        <v>0.3521451650925313</v>
+        <v>0.1764253036099144</v>
       </c>
       <c r="S166" t="n">
-        <v>6.028544072279443</v>
+        <v>63.98776015178731</v>
       </c>
       <c r="T166" t="n">
-        <v>165.8775299658532</v>
+        <v>15.62798881579648</v>
       </c>
       <c r="U166" t="inlineStr">
         <is>
@@ -16188,7 +16188,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -16221,37 +16221,37 @@
         </is>
       </c>
       <c r="J167" t="n">
-        <v>9.089143037796021</v>
+        <v>61.29265928268433</v>
       </c>
       <c r="K167" t="n">
-        <v>0.8729381786881008</v>
+        <v>0.8768088256656802</v>
       </c>
       <c r="L167" t="n">
-        <v>0.8975638762461614</v>
+        <v>0.8870875723134087</v>
       </c>
       <c r="M167" t="n">
-        <v>0.9344103520410754</v>
+        <v>0.9362675415983444</v>
       </c>
       <c r="N167" t="n">
-        <v>0.7952145538510431</v>
+        <v>0.808555114657571</v>
       </c>
       <c r="O167" t="n">
-        <v>0.7952145538510431</v>
+        <v>0.808555114657571</v>
       </c>
       <c r="P167" t="n">
-        <v>1.213023071072548</v>
+        <v>3.185828581927783</v>
       </c>
       <c r="Q167" t="n">
-        <v>3.805790138599205</v>
+        <v>62.11044081686062</v>
       </c>
       <c r="R167" t="n">
-        <v>0.3160019493724937</v>
+        <v>0.1901159879444861</v>
       </c>
       <c r="S167" t="n">
-        <v>5.334815159044246</v>
+        <v>65.48638538673288</v>
       </c>
       <c r="T167" t="n">
-        <v>187.4479190351469</v>
+        <v>15.2703496168624</v>
       </c>
       <c r="U167" t="inlineStr">
         <is>
@@ -16285,7 +16285,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -16318,37 +16318,37 @@
         </is>
       </c>
       <c r="J168" t="n">
-        <v>9.113104343414308</v>
+        <v>59.56893801689148</v>
       </c>
       <c r="K168" t="n">
-        <v>0.8729381786881008</v>
+        <v>0.8768088256656802</v>
       </c>
       <c r="L168" t="n">
-        <v>0.8975638762461614</v>
+        <v>0.8870875723134087</v>
       </c>
       <c r="M168" t="n">
-        <v>0.9344103520410754</v>
+        <v>0.9362675415983444</v>
       </c>
       <c r="N168" t="n">
-        <v>0.7952145538510431</v>
+        <v>0.808555114657571</v>
       </c>
       <c r="O168" t="n">
-        <v>0.7952145538510431</v>
+        <v>0.808555114657571</v>
       </c>
       <c r="P168" t="n">
-        <v>1.234613444598452</v>
+        <v>3.347849456626334</v>
       </c>
       <c r="Q168" t="n">
-        <v>3.879838393970795</v>
+        <v>61.25626890120493</v>
       </c>
       <c r="R168" t="n">
-        <v>0.3185821192970931</v>
+        <v>0.1960719313287937</v>
       </c>
       <c r="S168" t="n">
-        <v>5.43303395786634</v>
+        <v>64.80019028916004</v>
       </c>
       <c r="T168" t="n">
-        <v>184.059221377059</v>
+        <v>15.43205344826407</v>
       </c>
       <c r="U168" t="inlineStr">
         <is>
@@ -16382,7 +16382,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -16415,37 +16415,37 @@
         </is>
       </c>
       <c r="J169" t="n">
-        <v>9.975719928741457</v>
+        <v>58.88414597511292</v>
       </c>
       <c r="K169" t="n">
-        <v>0.8729381786881008</v>
+        <v>0.8768088256656802</v>
       </c>
       <c r="L169" t="n">
-        <v>0.8975638762461614</v>
+        <v>0.8870875723134087</v>
       </c>
       <c r="M169" t="n">
-        <v>0.9344103520410754</v>
+        <v>0.9362675415983444</v>
       </c>
       <c r="N169" t="n">
-        <v>0.7952145538510431</v>
+        <v>0.808555114657571</v>
       </c>
       <c r="O169" t="n">
-        <v>0.7952145538510431</v>
+        <v>0.808555114657571</v>
       </c>
       <c r="P169" t="n">
-        <v>1.331740408425843</v>
+        <v>3.251770795190256</v>
       </c>
       <c r="Q169" t="n">
-        <v>4.357297768676443</v>
+        <v>60.6550611361443</v>
       </c>
       <c r="R169" t="n">
-        <v>0.3365261108437076</v>
+        <v>0.1936560132555796</v>
       </c>
       <c r="S169" t="n">
-        <v>6.025564287945993</v>
+        <v>64.10048794459013</v>
       </c>
       <c r="T169" t="n">
-        <v>165.959560335366</v>
+        <v>15.60050527016927</v>
       </c>
       <c r="U169" t="inlineStr">
         <is>
@@ -16479,7 +16479,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -16512,37 +16512,37 @@
         </is>
       </c>
       <c r="J170" t="n">
-        <v>8.155663728713989</v>
+        <v>60.26346230506897</v>
       </c>
       <c r="K170" t="n">
-        <v>0.8707140569750392</v>
+        <v>0.8964423867891718</v>
       </c>
       <c r="L170" t="n">
-        <v>0.8522574775721816</v>
+        <v>0.8518205142742233</v>
       </c>
       <c r="M170" t="n">
-        <v>0.9083748763111515</v>
+        <v>0.9345543815455292</v>
       </c>
       <c r="N170" t="n">
-        <v>0.7699517482344933</v>
+        <v>0.8062458515669091</v>
       </c>
       <c r="O170" t="n">
-        <v>0.7699517482344933</v>
+        <v>0.8062458515669091</v>
       </c>
       <c r="P170" t="n">
-        <v>1.180629424121128</v>
+        <v>2.97798864938334</v>
       </c>
       <c r="Q170" t="n">
-        <v>3.429347692751862</v>
+        <v>61.4793184903581</v>
       </c>
       <c r="R170" t="n">
-        <v>0.3083778614886084</v>
+        <v>0.1960975228950745</v>
       </c>
       <c r="S170" t="n">
-        <v>4.918354978361599</v>
+        <v>64.6534046626365</v>
       </c>
       <c r="T170" t="n">
-        <v>203.3200133783592</v>
+        <v>15.46708955573232</v>
       </c>
       <c r="U170" t="inlineStr">
         <is>
@@ -16576,7 +16576,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -16609,37 +16609,37 @@
         </is>
       </c>
       <c r="J171" t="n">
-        <v>9.99750018119812</v>
+        <v>58.92950129508972</v>
       </c>
       <c r="K171" t="n">
-        <v>0.8707140569750392</v>
+        <v>0.8964423867891718</v>
       </c>
       <c r="L171" t="n">
-        <v>0.8522574775721816</v>
+        <v>0.8518205142742233</v>
       </c>
       <c r="M171" t="n">
-        <v>0.9083748763111515</v>
+        <v>0.9345543815455292</v>
       </c>
       <c r="N171" t="n">
-        <v>0.7699517482344933</v>
+        <v>0.8062458515669091</v>
       </c>
       <c r="O171" t="n">
-        <v>0.7699517482344933</v>
+        <v>0.8062458515669091</v>
       </c>
       <c r="P171" t="n">
-        <v>1.3723471843161</v>
+        <v>3.161754009643557</v>
       </c>
       <c r="Q171" t="n">
-        <v>4.394243479531812</v>
+        <v>60.90852873614045</v>
       </c>
       <c r="R171" t="n">
-        <v>0.3416154060643573</v>
+        <v>0.1978242156585921</v>
       </c>
       <c r="S171" t="n">
-        <v>6.108206069912269</v>
+        <v>64.26810696144261</v>
       </c>
       <c r="T171" t="n">
-        <v>163.7141885120393</v>
+        <v>15.55981726052622</v>
       </c>
       <c r="U171" t="inlineStr">
         <is>
@@ -16673,7 +16673,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -16706,37 +16706,37 @@
         </is>
       </c>
       <c r="J172" t="n">
-        <v>10.2380223274231</v>
+        <v>59.08849263191223</v>
       </c>
       <c r="K172" t="n">
-        <v>0.8707140569750392</v>
+        <v>0.8964423867891718</v>
       </c>
       <c r="L172" t="n">
-        <v>0.8522574775721816</v>
+        <v>0.8518205142742233</v>
       </c>
       <c r="M172" t="n">
-        <v>0.9083748763111515</v>
+        <v>0.9345543815455292</v>
       </c>
       <c r="N172" t="n">
-        <v>0.7699517482344933</v>
+        <v>0.8062458515669091</v>
       </c>
       <c r="O172" t="n">
-        <v>0.7699517482344933</v>
+        <v>0.8062458515669091</v>
       </c>
       <c r="P172" t="n">
-        <v>1.289885173462674</v>
+        <v>3.331985312055928</v>
       </c>
       <c r="Q172" t="n">
-        <v>4.420830131331683</v>
+        <v>60.94101171445811</v>
       </c>
       <c r="R172" t="n">
-        <v>0.3510638469576286</v>
+        <v>0.1949709096393289</v>
       </c>
       <c r="S172" t="n">
-        <v>6.061779151751985</v>
+        <v>64.46796793615336</v>
       </c>
       <c r="T172" t="n">
-        <v>164.9680687741615</v>
+        <v>15.51157934728705</v>
       </c>
       <c r="U172" t="inlineStr">
         <is>
@@ -16770,7 +16770,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -16803,37 +16803,37 @@
         </is>
       </c>
       <c r="J173" t="n">
-        <v>8.191219329833984</v>
+        <v>59.98239517211914</v>
       </c>
       <c r="K173" t="n">
-        <v>0.8888511745802176</v>
+        <v>0.9007242709230804</v>
       </c>
       <c r="L173" t="n">
-        <v>0.8423088650259938</v>
+        <v>0.8634411034374985</v>
       </c>
       <c r="M173" t="n">
-        <v>0.920816621002182</v>
+        <v>0.9232057676193612</v>
       </c>
       <c r="N173" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="O173" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="P173" t="n">
-        <v>1.168852561401643</v>
+        <v>3.083654514463328</v>
       </c>
       <c r="Q173" t="n">
-        <v>3.465931490374868</v>
+        <v>61.13945347229586</v>
       </c>
       <c r="R173" t="n">
-        <v>0.3117338686999836</v>
+        <v>0.1972950204831194</v>
       </c>
       <c r="S173" t="n">
-        <v>4.946517920476494</v>
+        <v>64.42040300724231</v>
       </c>
       <c r="T173" t="n">
-        <v>202.1624132524462</v>
+        <v>15.5230323518401</v>
       </c>
       <c r="U173" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -16900,37 +16900,37 @@
         </is>
       </c>
       <c r="J174" t="n">
-        <v>9.817988395690918</v>
+        <v>58.35378503799439</v>
       </c>
       <c r="K174" t="n">
-        <v>0.8888511745802176</v>
+        <v>0.9007242709230804</v>
       </c>
       <c r="L174" t="n">
-        <v>0.8423088650259938</v>
+        <v>0.8634411034374985</v>
       </c>
       <c r="M174" t="n">
-        <v>0.920816621002182</v>
+        <v>0.9232057676193612</v>
       </c>
       <c r="N174" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="O174" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="P174" t="n">
-        <v>1.258959024065018</v>
+        <v>2.20589367469918</v>
       </c>
       <c r="Q174" t="n">
-        <v>4.402442960211824</v>
+        <v>61.41809269757654</v>
       </c>
       <c r="R174" t="n">
-        <v>0.3507585229217292</v>
+        <v>0.1966948734941278</v>
       </c>
       <c r="S174" t="n">
-        <v>6.01216050719857</v>
+        <v>63.82068124576985</v>
       </c>
       <c r="T174" t="n">
-        <v>166.3295580353627</v>
+        <v>15.66890199979308</v>
       </c>
       <c r="U174" t="inlineStr">
         <is>
@@ -16964,7 +16964,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -16997,37 +16997,37 @@
         </is>
       </c>
       <c r="J175" t="n">
-        <v>8.79565954208374</v>
+        <v>59.64615654945374</v>
       </c>
       <c r="K175" t="n">
-        <v>0.8888511745802176</v>
+        <v>0.9007242709230804</v>
       </c>
       <c r="L175" t="n">
-        <v>0.8423088650259938</v>
+        <v>0.8634411034374985</v>
       </c>
       <c r="M175" t="n">
-        <v>0.920816621002182</v>
+        <v>0.9232057676193612</v>
       </c>
       <c r="N175" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="O175" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="P175" t="n">
-        <v>1.217432613242614</v>
+        <v>3.180622025290056</v>
       </c>
       <c r="Q175" t="n">
-        <v>3.726073743380394</v>
+        <v>61.74032578312481</v>
       </c>
       <c r="R175" t="n">
-        <v>0.3182634494060696</v>
+        <v>0.199364475915297</v>
       </c>
       <c r="S175" t="n">
-        <v>5.261769806029077</v>
+        <v>65.12031228433017</v>
       </c>
       <c r="T175" t="n">
-        <v>190.0501232216912</v>
+        <v>15.35619171532488</v>
       </c>
       <c r="U175" t="inlineStr">
         <is>
@@ -17061,7 +17061,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -17094,37 +17094,37 @@
         </is>
       </c>
       <c r="J176" t="n">
-        <v>9.296525001525881</v>
+        <v>60.03535008430481</v>
       </c>
       <c r="K176" t="n">
-        <v>0.8713330186365799</v>
+        <v>0.8894432429992767</v>
       </c>
       <c r="L176" t="n">
-        <v>0.8834321987481178</v>
+        <v>0.8632367360036634</v>
       </c>
       <c r="M176" t="n">
-        <v>0.9344102707423176</v>
+        <v>0.9324929045585608</v>
       </c>
       <c r="N176" t="n">
-        <v>0.7969907346365336</v>
+        <v>0.8003892058753374</v>
       </c>
       <c r="O176" t="n">
-        <v>0.7969907346365336</v>
+        <v>0.8003892058753374</v>
       </c>
       <c r="P176" t="n">
-        <v>1.254318056626618</v>
+        <v>3.022330383129818</v>
       </c>
       <c r="Q176" t="n">
-        <v>3.983685985532434</v>
+        <v>60.83191081083842</v>
       </c>
       <c r="R176" t="n">
-        <v>0.3192824216616334</v>
+        <v>0.1960494252901309</v>
       </c>
       <c r="S176" t="n">
-        <v>5.557286463820684</v>
+        <v>64.05029061925836</v>
       </c>
       <c r="T176" t="n">
-        <v>179.9439360396928</v>
+        <v>15.61273165713512</v>
       </c>
       <c r="U176" t="inlineStr">
         <is>
@@ -17158,7 +17158,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -17191,37 +17191,37 @@
         </is>
       </c>
       <c r="J177" t="n">
-        <v>10.09921073913574</v>
+        <v>58.71746230125427</v>
       </c>
       <c r="K177" t="n">
-        <v>0.8713330186365799</v>
+        <v>0.8894432429992767</v>
       </c>
       <c r="L177" t="n">
-        <v>0.8834321987481178</v>
+        <v>0.8632367360036634</v>
       </c>
       <c r="M177" t="n">
-        <v>0.9344102707423176</v>
+        <v>0.9324929045585608</v>
       </c>
       <c r="N177" t="n">
-        <v>0.7969907346365336</v>
+        <v>0.8003892058753374</v>
       </c>
       <c r="O177" t="n">
-        <v>0.7969907346365336</v>
+        <v>0.8003892058753374</v>
       </c>
       <c r="P177" t="n">
-        <v>1.348155501199723</v>
+        <v>3.174449668675327</v>
       </c>
       <c r="Q177" t="n">
-        <v>4.368008666259187</v>
+        <v>60.52263838673807</v>
       </c>
       <c r="R177" t="n">
-        <v>0.3434295385930629</v>
+        <v>0.1940091337358802</v>
       </c>
       <c r="S177" t="n">
-        <v>6.059593706051974</v>
+        <v>63.89109718914928</v>
       </c>
       <c r="T177" t="n">
-        <v>165.0275659573113</v>
+        <v>15.65163291905138</v>
       </c>
       <c r="U177" t="inlineStr">
         <is>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -17288,37 +17288,37 @@
         </is>
       </c>
       <c r="J178" t="n">
-        <v>8.495866537094116</v>
+        <v>59.45911145210266</v>
       </c>
       <c r="K178" t="n">
-        <v>0.8713330186365799</v>
+        <v>0.8894432429992767</v>
       </c>
       <c r="L178" t="n">
-        <v>0.8834321987481178</v>
+        <v>0.8632367360036634</v>
       </c>
       <c r="M178" t="n">
-        <v>0.9344102707423176</v>
+        <v>0.9324929045585608</v>
       </c>
       <c r="N178" t="n">
-        <v>0.7969907346365336</v>
+        <v>0.8003892058753374</v>
       </c>
       <c r="O178" t="n">
-        <v>0.7969907346365336</v>
+        <v>0.8003892058753374</v>
       </c>
       <c r="P178" t="n">
-        <v>1.191541687975072</v>
+        <v>3.193636939760332</v>
       </c>
       <c r="Q178" t="n">
-        <v>3.659971907216525</v>
+        <v>61.35913351927668</v>
       </c>
       <c r="R178" t="n">
-        <v>0.3118361048262772</v>
+        <v>0.1982441289060097</v>
       </c>
       <c r="S178" t="n">
-        <v>5.163349700017873</v>
+        <v>64.75101458794302</v>
       </c>
       <c r="T178" t="n">
-        <v>193.6727237352408</v>
+        <v>15.44377345071293</v>
       </c>
       <c r="U178" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -17385,37 +17385,37 @@
         </is>
       </c>
       <c r="J179" t="n">
-        <v>10.23582220077515</v>
+        <v>59.85925340652466</v>
       </c>
       <c r="K179" t="n">
-        <v>0.8626638400446858</v>
+        <v>0.8821708147587138</v>
       </c>
       <c r="L179" t="n">
-        <v>0.8994504233176549</v>
+        <v>0.8695893830757189</v>
       </c>
       <c r="M179" t="n">
-        <v>0.933442221253304</v>
+        <v>0.9286825537818112</v>
       </c>
       <c r="N179" t="n">
-        <v>0.8022050375687061</v>
+        <v>0.8024096003660925</v>
       </c>
       <c r="O179" t="n">
-        <v>0.8022050375687061</v>
+        <v>0.8024096003660925</v>
       </c>
       <c r="P179" t="n">
-        <v>1.354511483099574</v>
+        <v>2.748429346989856</v>
       </c>
       <c r="Q179" t="n">
-        <v>4.551339444554627</v>
+        <v>61.05294079395635</v>
       </c>
       <c r="R179" t="n">
-        <v>0.3435342987512444</v>
+        <v>0.1962123385603635</v>
       </c>
       <c r="S179" t="n">
-        <v>6.249385226405446</v>
+        <v>63.99758247950657</v>
       </c>
       <c r="T179" t="n">
-        <v>160.015739752242</v>
+        <v>15.6255902372597</v>
       </c>
       <c r="U179" t="inlineStr">
         <is>
@@ -17449,7 +17449,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -17482,37 +17482,37 @@
         </is>
       </c>
       <c r="J180" t="n">
-        <v>9.884141206741331</v>
+        <v>58.94184541702271</v>
       </c>
       <c r="K180" t="n">
-        <v>0.8626638400446858</v>
+        <v>0.8821708147587138</v>
       </c>
       <c r="L180" t="n">
-        <v>0.8994504233176549</v>
+        <v>0.8695893830757189</v>
       </c>
       <c r="M180" t="n">
-        <v>0.933442221253304</v>
+        <v>0.9286825537818112</v>
       </c>
       <c r="N180" t="n">
-        <v>0.8022050375687061</v>
+        <v>0.8024096003660925</v>
       </c>
       <c r="O180" t="n">
-        <v>0.8022050375687061</v>
+        <v>0.8024096003660925</v>
       </c>
       <c r="P180" t="n">
-        <v>1.320186569895427</v>
+        <v>3.185024238555672</v>
       </c>
       <c r="Q180" t="n">
-        <v>4.238427045819695</v>
+        <v>60.79805563854937</v>
       </c>
       <c r="R180" t="n">
-        <v>0.3313429987681145</v>
+        <v>0.1937291132495615</v>
       </c>
       <c r="S180" t="n">
-        <v>5.889956614483237</v>
+        <v>64.1768089903546</v>
       </c>
       <c r="T180" t="n">
-        <v>169.7805375239994</v>
+        <v>15.58195266689396</v>
       </c>
       <c r="U180" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -17579,37 +17579,37 @@
         </is>
       </c>
       <c r="J181" t="n">
-        <v>8.618870258331299</v>
+        <v>59.05126905441284</v>
       </c>
       <c r="K181" t="n">
-        <v>0.8626638400446858</v>
+        <v>0.8821708147587138</v>
       </c>
       <c r="L181" t="n">
-        <v>0.8994504233176549</v>
+        <v>0.8695893830757189</v>
       </c>
       <c r="M181" t="n">
-        <v>0.933442221253304</v>
+        <v>0.9286825537818112</v>
       </c>
       <c r="N181" t="n">
-        <v>0.8022050375687061</v>
+        <v>0.8024096003660925</v>
       </c>
       <c r="O181" t="n">
-        <v>0.8022050375687061</v>
+        <v>0.8024096003660925</v>
       </c>
       <c r="P181" t="n">
-        <v>1.200417616807926</v>
+        <v>2.223207268669132</v>
       </c>
       <c r="Q181" t="n">
-        <v>3.633441634975684</v>
+        <v>62.01846860723605</v>
       </c>
       <c r="R181" t="n">
-        <v>0.3113038506020837</v>
+        <v>0.1960108638565751</v>
       </c>
       <c r="S181" t="n">
-        <v>5.145163102385694</v>
+        <v>64.43768673976176</v>
       </c>
       <c r="T181" t="n">
-        <v>194.3572983208876</v>
+        <v>15.51886870238845</v>
       </c>
       <c r="U181" t="inlineStr">
         <is>
@@ -17643,7 +17643,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -17676,37 +17676,37 @@
         </is>
       </c>
       <c r="J182" t="n">
-        <v>10.06005048751831</v>
+        <v>60.76770091056824</v>
       </c>
       <c r="K182" t="n">
-        <v>0.8366387179945585</v>
+        <v>0.8662210580690296</v>
       </c>
       <c r="L182" t="n">
-        <v>0.8299938487051532</v>
+        <v>0.8412129116577401</v>
       </c>
       <c r="M182" t="n">
-        <v>0.9002848662126398</v>
+        <v>0.923541728741142</v>
       </c>
       <c r="N182" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416778</v>
       </c>
       <c r="O182" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416778</v>
       </c>
       <c r="P182" t="n">
-        <v>1.323305284309009</v>
+        <v>2.955306515659357</v>
       </c>
       <c r="Q182" t="n">
-        <v>4.536971578292365</v>
+        <v>61.96392989034953</v>
       </c>
       <c r="R182" t="n">
-        <v>0.329991133737375</v>
+        <v>0.1966932481892915</v>
       </c>
       <c r="S182" t="n">
-        <v>6.190267996338749</v>
+        <v>65.11592965419817</v>
       </c>
       <c r="T182" t="n">
-        <v>161.5438944794398</v>
+        <v>15.3572252643947</v>
       </c>
       <c r="U182" t="inlineStr">
         <is>
@@ -17740,7 +17740,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -17773,37 +17773,37 @@
         </is>
       </c>
       <c r="J183" t="n">
-        <v>9.060518503189089</v>
+        <v>60.72129988670349</v>
       </c>
       <c r="K183" t="n">
-        <v>0.8366387179945585</v>
+        <v>0.8662210580690296</v>
       </c>
       <c r="L183" t="n">
-        <v>0.8299938487051532</v>
+        <v>0.8412129116577401</v>
       </c>
       <c r="M183" t="n">
-        <v>0.9002848662126398</v>
+        <v>0.923541728741142</v>
       </c>
       <c r="N183" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416778</v>
       </c>
       <c r="O183" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416778</v>
       </c>
       <c r="P183" t="n">
-        <v>1.242350834976364</v>
+        <v>3.087567839757176</v>
       </c>
       <c r="Q183" t="n">
-        <v>3.878452881949067</v>
+        <v>62.31374739637946</v>
       </c>
       <c r="R183" t="n">
-        <v>0.319656326537808</v>
+        <v>0.1975734156624102</v>
       </c>
       <c r="S183" t="n">
-        <v>5.44046004346324</v>
+        <v>65.59888865179904</v>
       </c>
       <c r="T183" t="n">
-        <v>183.8079853562216</v>
+        <v>15.24416069467322</v>
       </c>
       <c r="U183" t="inlineStr">
         <is>
@@ -17837,7 +17837,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -17870,37 +17870,37 @@
         </is>
       </c>
       <c r="J184" t="n">
-        <v>9.675210237503052</v>
+        <v>60.51085138320923</v>
       </c>
       <c r="K184" t="n">
-        <v>0.8366387179945585</v>
+        <v>0.8662210580690296</v>
       </c>
       <c r="L184" t="n">
-        <v>0.8299938487051532</v>
+        <v>0.8412129116577401</v>
       </c>
       <c r="M184" t="n">
-        <v>0.9002848662126398</v>
+        <v>0.923541728741142</v>
       </c>
       <c r="N184" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416778</v>
       </c>
       <c r="O184" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416778</v>
       </c>
       <c r="P184" t="n">
-        <v>1.253963098839362</v>
+        <v>3.210709798797478</v>
       </c>
       <c r="Q184" t="n">
-        <v>4.264567971090783</v>
+        <v>61.95215227952736</v>
       </c>
       <c r="R184" t="n">
-        <v>0.3213423530274689</v>
+        <v>0.1968657578323385</v>
       </c>
       <c r="S184" t="n">
-        <v>5.839873422957614</v>
+        <v>65.35972783615718</v>
       </c>
       <c r="T184" t="n">
-        <v>171.2365881200124</v>
+        <v>15.29994131105909</v>
       </c>
       <c r="U184" t="inlineStr">
         <is>
@@ -17934,7 +17934,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -17967,37 +17967,37 @@
         </is>
       </c>
       <c r="J185" t="n">
-        <v>10.18562650680542</v>
+        <v>61.24172377586365</v>
       </c>
       <c r="K185" t="n">
-        <v>0.8179731363167645</v>
+        <v>0.8596283736711174</v>
       </c>
       <c r="L185" t="n">
-        <v>0.8614344192967365</v>
+        <v>0.8906635781698</v>
       </c>
       <c r="M185" t="n">
-        <v>0.9021413829153112</v>
+        <v>0.9307901364833598</v>
       </c>
       <c r="N185" t="n">
-        <v>0.7575501107005344</v>
+        <v>0.7837667125667425</v>
       </c>
       <c r="O185" t="n">
-        <v>0.7575501107005344</v>
+        <v>0.7837667125667425</v>
       </c>
       <c r="P185" t="n">
-        <v>1.353970868677355</v>
+        <v>3.05711818673773</v>
       </c>
       <c r="Q185" t="n">
-        <v>4.540262954215434</v>
+        <v>61.99581863132657</v>
       </c>
       <c r="R185" t="n">
-        <v>0.3652344819740217</v>
+        <v>0.1947455072317404</v>
       </c>
       <c r="S185" t="n">
-        <v>6.25946830486681</v>
+        <v>65.24768232529604</v>
       </c>
       <c r="T185" t="n">
-        <v>159.7579780414398</v>
+        <v>15.32621488399301</v>
       </c>
       <c r="U185" t="inlineStr">
         <is>
@@ -18031,7 +18031,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -18064,37 +18064,37 @@
         </is>
       </c>
       <c r="J186" t="n">
-        <v>8.409804105758667</v>
+        <v>60.31957316398621</v>
       </c>
       <c r="K186" t="n">
-        <v>0.8179731363167645</v>
+        <v>0.8596283736711174</v>
       </c>
       <c r="L186" t="n">
-        <v>0.8614344192967365</v>
+        <v>0.8906635781698</v>
       </c>
       <c r="M186" t="n">
-        <v>0.9021413829153112</v>
+        <v>0.9307901364833598</v>
       </c>
       <c r="N186" t="n">
-        <v>0.7575501107005344</v>
+        <v>0.7837667125667425</v>
       </c>
       <c r="O186" t="n">
-        <v>0.7575501107005344</v>
+        <v>0.7837667125667425</v>
       </c>
       <c r="P186" t="n">
-        <v>1.198618190381196</v>
+        <v>3.180057955422996</v>
       </c>
       <c r="Q186" t="n">
-        <v>3.54956285903109</v>
+        <v>62.49200188795807</v>
       </c>
       <c r="R186" t="n">
-        <v>0.3139827542239449</v>
+        <v>0.2000162108425322</v>
       </c>
       <c r="S186" t="n">
-        <v>5.06216380363623</v>
+        <v>65.8720760542236</v>
       </c>
       <c r="T186" t="n">
-        <v>197.5439829271594</v>
+        <v>15.18093947998291</v>
       </c>
       <c r="U186" t="inlineStr">
         <is>
@@ -18128,7 +18128,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -18161,37 +18161,37 @@
         </is>
       </c>
       <c r="J187" t="n">
-        <v>10.1173894405365</v>
+        <v>61.44903373718262</v>
       </c>
       <c r="K187" t="n">
-        <v>0.8179731363167645</v>
+        <v>0.8596283736711174</v>
       </c>
       <c r="L187" t="n">
-        <v>0.8614344192967365</v>
+        <v>0.8906635781698</v>
       </c>
       <c r="M187" t="n">
-        <v>0.9021413829153112</v>
+        <v>0.9307901364833598</v>
       </c>
       <c r="N187" t="n">
-        <v>0.7575501107005344</v>
+        <v>0.7837667125667425</v>
       </c>
       <c r="O187" t="n">
-        <v>0.7575501107005344</v>
+        <v>0.7837667125667425</v>
       </c>
       <c r="P187" t="n">
-        <v>1.325706149408831</v>
+        <v>3.391078795179252</v>
       </c>
       <c r="Q187" t="n">
-        <v>4.455786550575597</v>
+        <v>63.57149296024206</v>
       </c>
       <c r="R187" t="n">
-        <v>0.3435886433169755</v>
+        <v>0.203368862641407</v>
       </c>
       <c r="S187" t="n">
-        <v>6.125081343301403</v>
+        <v>67.16594061806272</v>
       </c>
       <c r="T187" t="n">
-        <v>163.2631378999781</v>
+        <v>14.88849840853823</v>
       </c>
       <c r="U187" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -18258,37 +18258,37 @@
         </is>
       </c>
       <c r="J188" t="n">
-        <v>10.02762985229492</v>
+        <v>60.53310775756836</v>
       </c>
       <c r="K188" t="n">
-        <v>0.7070219511570386</v>
+        <v>0.7958074694235807</v>
       </c>
       <c r="L188" t="n">
-        <v>0.6390600007387984</v>
+        <v>0.6532800973615224</v>
       </c>
       <c r="M188" t="n">
-        <v>0.7205195768217172</v>
+        <v>0.751252205640335</v>
       </c>
       <c r="N188" t="n">
-        <v>0.5475915817275469</v>
+        <v>0.5839382459240198</v>
       </c>
       <c r="O188" t="n">
-        <v>0.5475915817275469</v>
+        <v>0.5839382459240198</v>
       </c>
       <c r="P188" t="n">
-        <v>1.276974920521358</v>
+        <v>2.811398706029628</v>
       </c>
       <c r="Q188" t="n">
-        <v>4.449955990339621</v>
+        <v>62.38498326022976</v>
       </c>
       <c r="R188" t="n">
-        <v>0.3397417710698665</v>
+        <v>0.1978427023930701</v>
       </c>
       <c r="S188" t="n">
-        <v>6.066672681930846</v>
+        <v>65.39422466865246</v>
       </c>
       <c r="T188" t="n">
-        <v>164.8350013968001</v>
+        <v>15.29187026938424</v>
       </c>
       <c r="U188" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -18355,37 +18355,37 @@
         </is>
       </c>
       <c r="J189" t="n">
-        <v>8.502555131912231</v>
+        <v>59.51439237594604</v>
       </c>
       <c r="K189" t="n">
-        <v>0.7070219511570386</v>
+        <v>0.7958074694235807</v>
       </c>
       <c r="L189" t="n">
-        <v>0.6390600007387984</v>
+        <v>0.6532800973615224</v>
       </c>
       <c r="M189" t="n">
-        <v>0.7205195768217172</v>
+        <v>0.751252205640335</v>
       </c>
       <c r="N189" t="n">
-        <v>0.5475915817275469</v>
+        <v>0.5839382459240198</v>
       </c>
       <c r="O189" t="n">
-        <v>0.5475915817275469</v>
+        <v>0.5839382459240198</v>
       </c>
       <c r="P189" t="n">
-        <v>1.205356446954251</v>
+        <v>3.16815523733512</v>
       </c>
       <c r="Q189" t="n">
-        <v>3.696078893947096</v>
+        <v>61.75980855540762</v>
       </c>
       <c r="R189" t="n">
-        <v>0.3279016348982163</v>
+        <v>0.1943270421694492</v>
       </c>
       <c r="S189" t="n">
-        <v>5.229336975799563</v>
+        <v>65.12229083491218</v>
       </c>
       <c r="T189" t="n">
-        <v>191.2288316143751</v>
+        <v>15.35572516229571</v>
       </c>
       <c r="U189" t="inlineStr">
         <is>
@@ -18419,7 +18419,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -18452,37 +18452,37 @@
         </is>
       </c>
       <c r="J190" t="n">
-        <v>10.00291419029236</v>
+        <v>59.64236378669739</v>
       </c>
       <c r="K190" t="n">
-        <v>0.7070219511570386</v>
+        <v>0.7958074694235807</v>
       </c>
       <c r="L190" t="n">
-        <v>0.6390600007387984</v>
+        <v>0.6532800973615224</v>
       </c>
       <c r="M190" t="n">
-        <v>0.7205195768217172</v>
+        <v>0.751252205640335</v>
       </c>
       <c r="N190" t="n">
-        <v>0.5475915817275469</v>
+        <v>0.5839382459240198</v>
       </c>
       <c r="O190" t="n">
-        <v>0.5475915817275469</v>
+        <v>0.5839382459240198</v>
       </c>
       <c r="P190" t="n">
-        <v>1.25702875898625</v>
+        <v>3.258446079503465</v>
       </c>
       <c r="Q190" t="n">
-        <v>4.532991957815953</v>
+        <v>61.78047201445619</v>
       </c>
       <c r="R190" t="n">
-        <v>0.3341426999531356</v>
+        <v>0.1950430289268176</v>
       </c>
       <c r="S190" t="n">
-        <v>6.124163416755338</v>
+        <v>65.23396112288647</v>
       </c>
       <c r="T190" t="n">
-        <v>163.2876087636821</v>
+        <v>15.32943857442934</v>
       </c>
       <c r="U190" t="inlineStr">
         <is>
@@ -18516,7 +18516,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -18549,37 +18549,37 @@
         </is>
       </c>
       <c r="J191" t="n">
-        <v>9.153937816619871</v>
+        <v>60.10424399375916</v>
       </c>
       <c r="K191" t="n">
-        <v>0.435271050241385</v>
+        <v>0.4264367120104848</v>
       </c>
       <c r="L191" t="n">
-        <v>0.122124219307546</v>
+        <v>0.2174558723178378</v>
       </c>
       <c r="M191" t="n">
-        <v>0.1271027450111712</v>
+        <v>0.2184629615009358</v>
       </c>
       <c r="N191" t="n">
-        <v>0.07292086991843209</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="O191" t="n">
-        <v>0.07292086991843209</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="P191" t="n">
-        <v>1.249511292757321</v>
+        <v>2.674301946975113</v>
       </c>
       <c r="Q191" t="n">
-        <v>4.033442353003526</v>
+        <v>62.22300034939497</v>
       </c>
       <c r="R191" t="n">
-        <v>0.3289966337707669</v>
+        <v>0.1964590529945759</v>
       </c>
       <c r="S191" t="n">
-        <v>5.611950279531614</v>
+        <v>65.09376134936466</v>
       </c>
       <c r="T191" t="n">
-        <v>178.191172442722</v>
+        <v>15.36245531477128</v>
       </c>
       <c r="U191" t="inlineStr">
         <is>
@@ -18613,7 +18613,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -18646,37 +18646,37 @@
         </is>
       </c>
       <c r="J192" t="n">
-        <v>9.04016900062561</v>
+        <v>59.84819507598877</v>
       </c>
       <c r="K192" t="n">
-        <v>0.435271050241385</v>
+        <v>0.4264367120104848</v>
       </c>
       <c r="L192" t="n">
-        <v>0.122124219307546</v>
+        <v>0.2174558723178378</v>
       </c>
       <c r="M192" t="n">
-        <v>0.1271027450111712</v>
+        <v>0.2184629615009358</v>
       </c>
       <c r="N192" t="n">
-        <v>0.07292086991843209</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="O192" t="n">
-        <v>0.07292086991843209</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="P192" t="n">
-        <v>1.225113700016357</v>
+        <v>2.942382880705572</v>
       </c>
       <c r="Q192" t="n">
-        <v>3.98111584937254</v>
+        <v>62.62514821565203</v>
       </c>
       <c r="R192" t="n">
-        <v>0.3234090602427934</v>
+        <v>0.1982536879643385</v>
       </c>
       <c r="S192" t="n">
-        <v>5.52963860963169</v>
+        <v>65.76578478432194</v>
       </c>
       <c r="T192" t="n">
-        <v>180.8436446928322</v>
+        <v>15.20547505484026</v>
       </c>
       <c r="U192" t="inlineStr">
         <is>
@@ -18710,7 +18710,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best.engine</t>
+          <t>/content/drive/MyDrive/yolo_treinos/yolo26n_airplane_fp32/weights/best_int8_openvino_model</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -18743,37 +18743,37 @@
         </is>
       </c>
       <c r="J193" t="n">
-        <v>9.96558713912964</v>
+        <v>59.67401480674744</v>
       </c>
       <c r="K193" t="n">
-        <v>0.435271050241385</v>
+        <v>0.4264367120104848</v>
       </c>
       <c r="L193" t="n">
-        <v>0.122124219307546</v>
+        <v>0.2174558723178378</v>
       </c>
       <c r="M193" t="n">
-        <v>0.1271027450111712</v>
+        <v>0.2184629615009358</v>
       </c>
       <c r="N193" t="n">
-        <v>0.07292086991843209</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="O193" t="n">
-        <v>0.07292086991843209</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="P193" t="n">
-        <v>1.319577486719936</v>
+        <v>3.002698403597825</v>
       </c>
       <c r="Q193" t="n">
-        <v>4.397309184305304</v>
+        <v>62.33669640362469</v>
       </c>
       <c r="R193" t="n">
-        <v>0.3338473891514684</v>
+        <v>0.1961259855525862</v>
       </c>
       <c r="S193" t="n">
-        <v>6.050734060176709</v>
+        <v>65.5355207927751</v>
       </c>
       <c r="T193" t="n">
-        <v>165.269203712251</v>
+        <v>15.25890063744247</v>
       </c>
       <c r="U193" t="inlineStr">
         <is>
@@ -28103,130 +28103,130 @@
         </is>
       </c>
       <c r="I50" t="n">
-        <v>0.8963520100241514</v>
+        <v>0.8861158550177132</v>
       </c>
       <c r="J50" t="n">
         <v>0</v>
       </c>
       <c r="K50" t="n">
-        <v>0.8963520100241514</v>
+        <v>0.8861158550177131</v>
       </c>
       <c r="L50" t="n">
-        <v>0.8963520100241514</v>
+        <v>0.8861158550177131</v>
       </c>
       <c r="M50" t="n">
-        <v>0.8660765626746049</v>
+        <v>0.8829669114684049</v>
       </c>
       <c r="N50" t="n">
         <v>0</v>
       </c>
       <c r="O50" t="n">
-        <v>0.8660765626746049</v>
+        <v>0.8829669114684049</v>
       </c>
       <c r="P50" t="n">
-        <v>0.8660765626746049</v>
+        <v>0.8829669114684049</v>
       </c>
       <c r="Q50" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="R50" t="n">
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="T50" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="U50" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
       </c>
       <c r="W50" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="X50" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="Y50" t="n">
-        <v>1.195114706416027</v>
+        <v>3.459603306828011</v>
       </c>
       <c r="Z50" t="n">
-        <v>0.07245072200281331</v>
+        <v>0.1029811123327931</v>
       </c>
       <c r="AA50" t="n">
-        <v>1.11392816382589</v>
+        <v>3.389318269883992</v>
       </c>
       <c r="AB50" t="n">
-        <v>1.253191286763555</v>
+        <v>3.577812784336889</v>
       </c>
       <c r="AC50" t="n">
-        <v>3.739857279515308</v>
+        <v>62.7695173104398</v>
       </c>
       <c r="AD50" t="n">
-        <v>0.4305006474917559</v>
+        <v>0.8454500031771928</v>
       </c>
       <c r="AE50" t="n">
-        <v>3.331245740935037</v>
+        <v>62.19613654096213</v>
       </c>
       <c r="AF50" t="n">
-        <v>4.189332919293476</v>
+        <v>63.74046757107902</v>
       </c>
       <c r="AG50" t="n">
-        <v>0.3214192212893919</v>
+        <v>0.1961919489942199</v>
       </c>
       <c r="AH50" t="n">
-        <v>0.02057036352137559</v>
+        <v>0.002596063948170386</v>
       </c>
       <c r="AI50" t="n">
-        <v>0.2981121217024075</v>
+        <v>0.1931943999960526</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0.3370381445877804</v>
+        <v>0.1977146614480952</v>
       </c>
       <c r="AK50" t="n">
-        <v>5.256391207220727</v>
+        <v>66.42531256626202</v>
       </c>
       <c r="AL50" t="n">
-        <v>0.5182114893728951</v>
+        <v>0.8007284624570832</v>
       </c>
       <c r="AM50" t="n">
-        <v>4.743286026463334</v>
+        <v>65.95446048915828</v>
       </c>
       <c r="AN50" t="n">
-        <v>5.779562350644812</v>
+        <v>67.34986109879026</v>
       </c>
       <c r="AO50" t="n">
-        <v>191.4857997151397</v>
+        <v>15.05595045746269</v>
       </c>
       <c r="AP50" t="n">
-        <v>18.91563971862029</v>
+        <v>0.1802392310244332</v>
       </c>
       <c r="AQ50" t="n">
-        <v>173.023481594317</v>
+        <v>14.84784056990374</v>
       </c>
       <c r="AR50" t="n">
-        <v>210.824309228009</v>
+        <v>15.16197680313649</v>
       </c>
       <c r="AS50" t="n">
-        <v>8.783390124638876</v>
+        <v>60.83974011739095</v>
       </c>
       <c r="AT50" t="n">
-        <v>0.8521905829646145</v>
+        <v>0.9823820398093274</v>
       </c>
       <c r="AU50" t="n">
-        <v>7.919425487518311</v>
+        <v>60.18165683746338</v>
       </c>
       <c r="AV50" t="n">
-        <v>9.623297214508057</v>
+        <v>61.96895003318787</v>
       </c>
       <c r="AW50" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX50" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY50" t="n">
         <v>0</v>
@@ -28241,10 +28241,10 @@
         <v>97.3445537305448</v>
       </c>
       <c r="BC50" t="n">
-        <v>18.63826646505563</v>
+        <v>1.465470635046152</v>
       </c>
       <c r="BD50" t="n">
-        <v>94.60022055083768</v>
+        <v>31.76268212176408</v>
       </c>
       <c r="BE50" t="n">
         <v>3</v>
@@ -28291,136 +28291,136 @@
         </is>
       </c>
       <c r="I51" t="n">
-        <v>0.8526107293020054</v>
+        <v>0.8554559725472815</v>
       </c>
       <c r="J51" t="n">
         <v>0</v>
       </c>
       <c r="K51" t="n">
-        <v>0.8526107293020055</v>
+        <v>0.8554559725472815</v>
       </c>
       <c r="L51" t="n">
-        <v>0.8526107293020055</v>
+        <v>0.8554559725472815</v>
       </c>
       <c r="M51" t="n">
-        <v>0.8344556377524764</v>
+        <v>0.846616077472835</v>
       </c>
       <c r="N51" t="n">
         <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>0.8344556377524764</v>
+        <v>0.8466160774728351</v>
       </c>
       <c r="P51" t="n">
-        <v>0.8344556377524764</v>
+        <v>0.8466160774728351</v>
       </c>
       <c r="Q51" t="n">
-        <v>0.8972129987083401</v>
+        <v>0.9138390369805568</v>
       </c>
       <c r="R51" t="n">
         <v>0</v>
       </c>
       <c r="S51" t="n">
-        <v>0.8972129987083401</v>
+        <v>0.9138390369805568</v>
       </c>
       <c r="T51" t="n">
-        <v>0.8972129987083401</v>
+        <v>0.9138390369805568</v>
       </c>
       <c r="U51" t="n">
-        <v>0.7578056823174325</v>
+        <v>0.779266846434712</v>
       </c>
       <c r="V51" t="n">
         <v>0</v>
       </c>
       <c r="W51" t="n">
-        <v>0.7578056823174325</v>
+        <v>0.7792668464347121</v>
       </c>
       <c r="X51" t="n">
-        <v>0.7578056823174325</v>
+        <v>0.7792668464347121</v>
       </c>
       <c r="Y51" t="n">
-        <v>1.198697713640052</v>
+        <v>3.147603802807841</v>
       </c>
       <c r="Z51" t="n">
-        <v>0.04588698018089592</v>
+        <v>0.2858501525158397</v>
       </c>
       <c r="AA51" t="n">
-        <v>1.166719560232118</v>
+        <v>2.823422363845917</v>
       </c>
       <c r="AB51" t="n">
-        <v>1.251274537317369</v>
+        <v>3.363454225299152</v>
       </c>
       <c r="AC51" t="n">
-        <v>3.791752829721121</v>
+        <v>62.62943875421558</v>
       </c>
       <c r="AD51" t="n">
-        <v>0.4513562730217205</v>
+        <v>0.807629141541976</v>
       </c>
       <c r="AE51" t="n">
-        <v>3.455434873495801</v>
+        <v>61.99228953855325</v>
       </c>
       <c r="AF51" t="n">
-        <v>4.304716331348737</v>
+        <v>63.5377552445712</v>
       </c>
       <c r="AG51" t="n">
-        <v>0.328459926089979</v>
+        <v>0.1924473698781765</v>
       </c>
       <c r="AH51" t="n">
-        <v>0.00771098586074569</v>
+        <v>0.0001658623182433498</v>
       </c>
       <c r="AI51" t="n">
-        <v>0.3199979036417719</v>
+        <v>0.1923058012109147</v>
       </c>
       <c r="AJ51" t="n">
-        <v>0.3350898818755823</v>
+        <v>0.1926298638485911</v>
       </c>
       <c r="AK51" t="n">
-        <v>5.318910469451152</v>
+        <v>65.9694899269016</v>
       </c>
       <c r="AL51" t="n">
-        <v>0.5037417138936777</v>
+        <v>1.05217026570697</v>
       </c>
       <c r="AM51" t="n">
-        <v>4.942152337369691</v>
+        <v>65.0081183469742</v>
       </c>
       <c r="AN51" t="n">
-        <v>5.891080750541688</v>
+        <v>67.09351527108127</v>
       </c>
       <c r="AO51" t="n">
-        <v>189.0894238198177</v>
+        <v>15.16108460988195</v>
       </c>
       <c r="AP51" t="n">
-        <v>17.12854250288773</v>
+        <v>0.2409656019529471</v>
       </c>
       <c r="AQ51" t="n">
-        <v>169.7481400009751</v>
+        <v>14.90457007595518</v>
       </c>
       <c r="AR51" t="n">
-        <v>202.3409906729462</v>
+        <v>15.38269412233411</v>
       </c>
       <c r="AS51" t="n">
-        <v>9.128423690795898</v>
+        <v>61.0341280301412</v>
       </c>
       <c r="AT51" t="n">
-        <v>0.6301827530281826</v>
+        <v>0.659090437052864</v>
       </c>
       <c r="AU51" t="n">
-        <v>8.508018255233765</v>
+        <v>60.29372668266296</v>
       </c>
       <c r="AV51" t="n">
-        <v>9.767948627471924</v>
+        <v>61.55682325363159</v>
       </c>
       <c r="AW51" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX51" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY51" t="n">
-        <v>4.08762347630109</v>
+        <v>2.525741423710154</v>
       </c>
       <c r="AZ51" t="n">
-        <v>5.764059995204061</v>
+        <v>3.867732821782958</v>
       </c>
       <c r="BA51" t="n">
         <v>10.53680734680013</v>
@@ -28429,10 +28429,10 @@
         <v>94.91308181887729</v>
       </c>
       <c r="BC51" t="n">
-        <v>17.94560891134081</v>
+        <v>1.4388689202414</v>
       </c>
       <c r="BD51" t="n">
-        <v>94.39601963446805</v>
+        <v>30.49483942288247</v>
       </c>
       <c r="BE51" t="n">
         <v>3</v>
@@ -28479,136 +28479,136 @@
         </is>
       </c>
       <c r="I52" t="n">
-        <v>0.725789278693295</v>
+        <v>0.7588249804831326</v>
       </c>
       <c r="J52" t="n">
         <v>0</v>
       </c>
       <c r="K52" t="n">
-        <v>0.725789278693295</v>
+        <v>0.7588249804831326</v>
       </c>
       <c r="L52" t="n">
-        <v>0.725789278693295</v>
+        <v>0.7588249804831326</v>
       </c>
       <c r="M52" t="n">
-        <v>0.728604791515712</v>
+        <v>0.7149502064942949</v>
       </c>
       <c r="N52" t="n">
         <v>0</v>
       </c>
       <c r="O52" t="n">
-        <v>0.7286047915157121</v>
+        <v>0.7149502064942947</v>
       </c>
       <c r="P52" t="n">
-        <v>0.7286047915157121</v>
+        <v>0.7149502064942947</v>
       </c>
       <c r="Q52" t="n">
-        <v>0.7707737698172715</v>
+        <v>0.7787717652837904</v>
       </c>
       <c r="R52" t="n">
         <v>0</v>
       </c>
       <c r="S52" t="n">
-        <v>0.7707737698172715</v>
+        <v>0.7787717652837904</v>
       </c>
       <c r="T52" t="n">
-        <v>0.7707737698172715</v>
+        <v>0.7787717652837904</v>
       </c>
       <c r="U52" t="n">
-        <v>0.6240064954710411</v>
+        <v>0.6254110464216518</v>
       </c>
       <c r="V52" t="n">
         <v>0</v>
       </c>
       <c r="W52" t="n">
-        <v>0.6240064954710411</v>
+        <v>0.6254110464216518</v>
       </c>
       <c r="X52" t="n">
-        <v>0.6240064954710411</v>
+        <v>0.6254110464216518</v>
       </c>
       <c r="Y52" t="n">
-        <v>1.244322522499686</v>
+        <v>3.235233858635618</v>
       </c>
       <c r="Z52" t="n">
-        <v>0.06976887124935006</v>
+        <v>0.1714013747493034</v>
       </c>
       <c r="AA52" t="n">
-        <v>1.167614981910359</v>
+        <v>3.082908084335546</v>
       </c>
       <c r="AB52" t="n">
-        <v>1.303999057811133</v>
+        <v>3.42083200120576</v>
       </c>
       <c r="AC52" t="n">
-        <v>3.922959594782729</v>
+        <v>64.50529935341301</v>
       </c>
       <c r="AD52" t="n">
-        <v>0.4561247068948571</v>
+        <v>1.308210807478817</v>
       </c>
       <c r="AE52" t="n">
-        <v>3.40827184698421</v>
+        <v>63.68552276024423</v>
       </c>
       <c r="AF52" t="n">
-        <v>4.277113281921585</v>
+        <v>66.0140007686731</v>
       </c>
       <c r="AG52" t="n">
-        <v>0.3306975646797312</v>
+        <v>0.1957951481963537</v>
       </c>
       <c r="AH52" t="n">
-        <v>0.02461973069973278</v>
+        <v>0.005125253734806275</v>
       </c>
       <c r="AI52" t="n">
-        <v>0.3071769952105361</v>
+        <v>0.1913050385621361</v>
       </c>
       <c r="AJ52" t="n">
-        <v>0.3562860180787232</v>
+        <v>0.201378977107449</v>
       </c>
       <c r="AK52" t="n">
-        <v>5.497979681962146</v>
+        <v>67.93632836024499</v>
       </c>
       <c r="AL52" t="n">
-        <v>0.5486390187645549</v>
+        <v>1.477580139081936</v>
       </c>
       <c r="AM52" t="n">
-        <v>4.883063824105106</v>
+        <v>66.9597358831419</v>
       </c>
       <c r="AN52" t="n">
-        <v>5.937398357811441</v>
+        <v>69.63621174698631</v>
       </c>
       <c r="AO52" t="n">
-        <v>183.1573852046965</v>
+        <v>14.72425285512592</v>
       </c>
       <c r="AP52" t="n">
-        <v>19.13912458950384</v>
+        <v>0.3164076682736824</v>
       </c>
       <c r="AQ52" t="n">
-        <v>168.4239358277799</v>
+        <v>14.36034463840974</v>
       </c>
       <c r="AR52" t="n">
-        <v>204.7894592455516</v>
+        <v>14.9343480348429</v>
       </c>
       <c r="AS52" t="n">
-        <v>9.108398040135702</v>
+        <v>62.95878370602926</v>
       </c>
       <c r="AT52" t="n">
-        <v>0.9068367328362542</v>
+        <v>1.040507951231619</v>
       </c>
       <c r="AU52" t="n">
-        <v>8.069807767868042</v>
+        <v>61.92353343963623</v>
       </c>
       <c r="AV52" t="n">
-        <v>9.743237733840942</v>
+        <v>64.00447082519531</v>
       </c>
       <c r="AW52" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX52" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY52" t="n">
-        <v>17.6040203031693</v>
+        <v>16.9326354540477</v>
       </c>
       <c r="AZ52" t="n">
-        <v>22.40248385313634</v>
+        <v>22.84776121827268</v>
       </c>
       <c r="BA52" t="n">
         <v>10.4272730580995</v>
@@ -28617,10 +28617,10 @@
         <v>95.92040201003137</v>
       </c>
       <c r="BC52" t="n">
-        <v>17.56522383025416</v>
+        <v>1.412090464408496</v>
       </c>
       <c r="BD52" t="n">
-        <v>94.26818532163036</v>
+        <v>29.1742664369357</v>
       </c>
       <c r="BE52" t="n">
         <v>3</v>
@@ -28667,136 +28667,136 @@
         </is>
       </c>
       <c r="I53" t="n">
-        <v>0.6807838867983227</v>
+        <v>0.6299930781790891</v>
       </c>
       <c r="J53" t="n">
         <v>0</v>
       </c>
       <c r="K53" t="n">
-        <v>0.6807838867983227</v>
+        <v>0.6299930781790891</v>
       </c>
       <c r="L53" t="n">
-        <v>0.6807838867983227</v>
+        <v>0.6299930781790891</v>
       </c>
       <c r="M53" t="n">
-        <v>0.4938162375024422</v>
+        <v>0.5236990023280943</v>
       </c>
       <c r="N53" t="n">
         <v>0</v>
       </c>
       <c r="O53" t="n">
-        <v>0.4938162375024422</v>
+        <v>0.5236990023280943</v>
       </c>
       <c r="P53" t="n">
-        <v>0.4938162375024422</v>
+        <v>0.5236990023280943</v>
       </c>
       <c r="Q53" t="n">
-        <v>0.5214984470712496</v>
+        <v>0.5807748643741676</v>
       </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
       <c r="S53" t="n">
-        <v>0.5214984470712496</v>
+        <v>0.5807748643741676</v>
       </c>
       <c r="T53" t="n">
-        <v>0.5214984470712496</v>
+        <v>0.5807748643741676</v>
       </c>
       <c r="U53" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="V53" t="n">
         <v>0</v>
       </c>
       <c r="W53" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="X53" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="Y53" t="n">
-        <v>1.240890381119375</v>
+        <v>3.07401487108204</v>
       </c>
       <c r="Z53" t="n">
-        <v>0.02291066127572707</v>
+        <v>0.03963301017321692</v>
       </c>
       <c r="AA53" t="n">
-        <v>1.215600822889614</v>
+        <v>3.035289937345197</v>
       </c>
       <c r="AB53" t="n">
-        <v>1.260260268671951</v>
+        <v>3.114497473501593</v>
       </c>
       <c r="AC53" t="n">
-        <v>4.036811780340313</v>
+        <v>61.68362194618701</v>
       </c>
       <c r="AD53" t="n">
-        <v>0.1936570828221393</v>
+        <v>2.622065695103189</v>
       </c>
       <c r="AE53" t="n">
-        <v>3.836754749436405</v>
+        <v>60.14954761686918</v>
       </c>
       <c r="AF53" t="n">
-        <v>4.223361703643824</v>
+        <v>64.71123215180988</v>
       </c>
       <c r="AG53" t="n">
-        <v>0.343587698396542</v>
+        <v>0.1885085064330554</v>
       </c>
       <c r="AH53" t="n">
-        <v>0.02059602669422079</v>
+        <v>0.001975656568859066</v>
       </c>
       <c r="AI53" t="n">
-        <v>0.3256693349744253</v>
+        <v>0.1863357096445692</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0.3660892397540492</v>
+        <v>0.1901969301299511</v>
       </c>
       <c r="AK53" t="n">
-        <v>5.621289859856229</v>
+        <v>64.94614532370211</v>
       </c>
       <c r="AL53" t="n">
-        <v>0.2304245714581085</v>
+        <v>2.65850857002784</v>
       </c>
       <c r="AM53" t="n">
-        <v>5.378024907300444</v>
+        <v>63.41079769879315</v>
       </c>
       <c r="AN53" t="n">
-        <v>5.836260995194432</v>
+        <v>68.01592655544142</v>
       </c>
       <c r="AO53" t="n">
-        <v>178.0962129130423</v>
+        <v>15.41419372853648</v>
       </c>
       <c r="AP53" t="n">
-        <v>7.360652628863323</v>
+        <v>0.6163978293862388</v>
       </c>
       <c r="AQ53" t="n">
-        <v>171.3425771779909</v>
+        <v>14.70243883518775</v>
       </c>
       <c r="AR53" t="n">
-        <v>185.941868480851</v>
+        <v>15.77018483114008</v>
       </c>
       <c r="AS53" t="n">
-        <v>9.47118059794108</v>
+        <v>60.12889409065247</v>
       </c>
       <c r="AT53" t="n">
-        <v>0.3487614145643093</v>
+        <v>2.789103668801163</v>
       </c>
       <c r="AU53" t="n">
-        <v>9.07709002494812</v>
+        <v>58.4327507019043</v>
       </c>
       <c r="AV53" t="n">
-        <v>9.740017175674438</v>
+        <v>63.34791970252991</v>
       </c>
       <c r="AW53" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX53" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY53" t="n">
-        <v>44.25163758881126</v>
+        <v>38.0518920578551</v>
       </c>
       <c r="AZ53" t="n">
-        <v>53.69159129775718</v>
+        <v>49.80363132446787</v>
       </c>
       <c r="BA53" t="n">
         <v>10.46560356014806</v>
@@ -28805,10 +28805,10 @@
         <v>95.55230161727472</v>
       </c>
       <c r="BC53" t="n">
-        <v>17.01729020113224</v>
+        <v>1.472843266033136</v>
       </c>
       <c r="BD53" t="n">
-        <v>94.11705446680735</v>
+        <v>32.03078918618051</v>
       </c>
       <c r="BE53" t="n">
         <v>3</v>
@@ -28855,136 +28855,136 @@
         </is>
       </c>
       <c r="I54" t="n">
-        <v>0.9111316364542188</v>
+        <v>0.9165630081374349</v>
       </c>
       <c r="J54" t="n">
         <v>0</v>
       </c>
       <c r="K54" t="n">
-        <v>0.9111316364542188</v>
+        <v>0.9165630081374349</v>
       </c>
       <c r="L54" t="n">
-        <v>0.9111316364542188</v>
+        <v>0.9165630081374349</v>
       </c>
       <c r="M54" t="n">
-        <v>0.8496529487895471</v>
+        <v>0.8429371880628344</v>
       </c>
       <c r="N54" t="n">
         <v>0</v>
       </c>
       <c r="O54" t="n">
-        <v>0.8496529487895471</v>
+        <v>0.8429371880628344</v>
       </c>
       <c r="P54" t="n">
-        <v>0.8496529487895471</v>
+        <v>0.8429371880628344</v>
       </c>
       <c r="Q54" t="n">
-        <v>0.9183375572963554</v>
+        <v>0.9190307552534428</v>
       </c>
       <c r="R54" t="n">
         <v>0</v>
       </c>
       <c r="S54" t="n">
-        <v>0.9183375572963552</v>
+        <v>0.9190307552534428</v>
       </c>
       <c r="T54" t="n">
-        <v>0.9183375572963552</v>
+        <v>0.9190307552534428</v>
       </c>
       <c r="U54" t="n">
-        <v>0.7868302589310699</v>
+        <v>0.7960427176781358</v>
       </c>
       <c r="V54" t="n">
         <v>0</v>
       </c>
       <c r="W54" t="n">
-        <v>0.7868302589310699</v>
+        <v>0.7960427176781357</v>
       </c>
       <c r="X54" t="n">
-        <v>0.7868302589310699</v>
+        <v>0.7960427176781357</v>
       </c>
       <c r="Y54" t="n">
-        <v>1.233937516895003</v>
+        <v>3.12459249478681</v>
       </c>
       <c r="Z54" t="n">
-        <v>0.03695803032341279</v>
+        <v>0.1645483319347854</v>
       </c>
       <c r="AA54" t="n">
-        <v>1.194461401231031</v>
+        <v>2.939649191577416</v>
       </c>
       <c r="AB54" t="n">
-        <v>1.267715632577647</v>
+        <v>3.254788601205576</v>
       </c>
       <c r="AC54" t="n">
-        <v>4.12386766706969</v>
+        <v>59.31604189156578</v>
       </c>
       <c r="AD54" t="n">
-        <v>0.3265875138509676</v>
+        <v>0.1340920400448596</v>
       </c>
       <c r="AE54" t="n">
-        <v>3.783325237326422</v>
+        <v>59.18442078434263</v>
       </c>
       <c r="AF54" t="n">
-        <v>4.43443337350022</v>
+        <v>59.45247530481505</v>
       </c>
       <c r="AG54" t="n">
-        <v>0.3438591703149676</v>
+        <v>0.1865343265050676</v>
       </c>
       <c r="AH54" t="n">
-        <v>0.02026736378702856</v>
+        <v>0.002876373316166548</v>
       </c>
       <c r="AI54" t="n">
-        <v>0.3299652867877213</v>
+        <v>0.1847110012005876</v>
       </c>
       <c r="AJ54" t="n">
-        <v>0.3671151903871354</v>
+        <v>0.1898501807219478</v>
       </c>
       <c r="AK54" t="n">
-        <v>5.701664354279661</v>
+        <v>62.62716871285766</v>
       </c>
       <c r="AL54" t="n">
-        <v>0.378960000813521</v>
+        <v>0.1880849568622517</v>
       </c>
       <c r="AM54" t="n">
-        <v>5.312283672327498</v>
+        <v>62.44072895783903</v>
       </c>
       <c r="AN54" t="n">
-        <v>6.069264196465003</v>
+        <v>62.81685679398516</v>
       </c>
       <c r="AO54" t="n">
-        <v>175.9091726081195</v>
+        <v>15.96760692109466</v>
       </c>
       <c r="AP54" t="n">
-        <v>11.78426193574862</v>
+        <v>0.0479511794357762</v>
       </c>
       <c r="AQ54" t="n">
-        <v>164.7646185154442</v>
+        <v>15.91929381757528</v>
       </c>
       <c r="AR54" t="n">
-        <v>188.2429594656539</v>
+        <v>16.01518778993141</v>
       </c>
       <c r="AS54" t="n">
-        <v>9.572548309961954</v>
+        <v>58.54720703760783</v>
       </c>
       <c r="AT54" t="n">
-        <v>0.5955514802352253</v>
+        <v>0.5739555021291043</v>
       </c>
       <c r="AU54" t="n">
-        <v>8.955272197723389</v>
+        <v>58.07856726646423</v>
       </c>
       <c r="AV54" t="n">
-        <v>10.14369201660156</v>
+        <v>59.18736863136292</v>
       </c>
       <c r="AW54" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX54" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.829400935937199</v>
+        <v>1.97196896608061</v>
       </c>
       <c r="AZ54" t="n">
-        <v>2.154746520458132</v>
+        <v>1.798220248652718</v>
       </c>
       <c r="BA54" t="n">
         <v>10.09997533796985</v>
@@ -28993,10 +28993,10 @@
         <v>99.06564576586976</v>
       </c>
       <c r="BC54" t="n">
-        <v>17.41679229124517</v>
+        <v>1.580955040658965</v>
       </c>
       <c r="BD54" t="n">
-        <v>94.2445594431849</v>
+        <v>36.78215265373654</v>
       </c>
       <c r="BE54" t="n">
         <v>3</v>
@@ -29043,136 +29043,136 @@
         </is>
       </c>
       <c r="I55" t="n">
-        <v>0.885160432857265</v>
+        <v>0.8017734960824066</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
       </c>
       <c r="K55" t="n">
-        <v>0.8851604328572649</v>
+        <v>0.8017734960824066</v>
       </c>
       <c r="L55" t="n">
-        <v>0.8851604328572649</v>
+        <v>0.8017734960824066</v>
       </c>
       <c r="M55" t="n">
-        <v>0.8277690110699493</v>
+        <v>0.8940013709838216</v>
       </c>
       <c r="N55" t="n">
         <v>0</v>
       </c>
       <c r="O55" t="n">
-        <v>0.8277690110699493</v>
+        <v>0.8940013709838216</v>
       </c>
       <c r="P55" t="n">
-        <v>0.8277690110699493</v>
+        <v>0.8940013709838216</v>
       </c>
       <c r="Q55" t="n">
-        <v>0.8903329101751702</v>
+        <v>0.9007055798541789</v>
       </c>
       <c r="R55" t="n">
         <v>0</v>
       </c>
       <c r="S55" t="n">
-        <v>0.8903329101751702</v>
+        <v>0.9007055798541789</v>
       </c>
       <c r="T55" t="n">
-        <v>0.8903329101751702</v>
+        <v>0.9007055798541789</v>
       </c>
       <c r="U55" t="n">
-        <v>0.7480057530889145</v>
+        <v>0.7730690891765476</v>
       </c>
       <c r="V55" t="n">
         <v>0</v>
       </c>
       <c r="W55" t="n">
-        <v>0.7480057530889146</v>
+        <v>0.7730690891765476</v>
       </c>
       <c r="X55" t="n">
-        <v>0.7480057530889146</v>
+        <v>0.7730690891765476</v>
       </c>
       <c r="Y55" t="n">
-        <v>1.253053451801975</v>
+        <v>2.88605877228683</v>
       </c>
       <c r="Z55" t="n">
-        <v>0.07108257482444742</v>
+        <v>0.5449305196675466</v>
       </c>
       <c r="AA55" t="n">
-        <v>1.174304463906499</v>
+        <v>2.257072510839687</v>
       </c>
       <c r="AB55" t="n">
-        <v>1.312469904804452</v>
+        <v>3.215766483129531</v>
       </c>
       <c r="AC55" t="n">
-        <v>4.075541675484714</v>
+        <v>60.82256200683073</v>
       </c>
       <c r="AD55" t="n">
-        <v>0.5882792812434716</v>
+        <v>0.9553152065438445</v>
       </c>
       <c r="AE55" t="n">
-        <v>3.402678697609398</v>
+        <v>59.76109326506629</v>
       </c>
       <c r="AF55" t="n">
-        <v>4.492682968621779</v>
+        <v>61.61327758193101</v>
       </c>
       <c r="AG55" t="n">
-        <v>0.3340860526322904</v>
+        <v>0.1923497907624317</v>
       </c>
       <c r="AH55" t="n">
-        <v>0.0284356888187775</v>
+        <v>0.0005453828551252168</v>
       </c>
       <c r="AI55" t="n">
-        <v>0.3022753277540884</v>
+        <v>0.1917534168728433</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0.3570374590423623</v>
+        <v>0.1928231807224039</v>
       </c>
       <c r="AK55" t="n">
-        <v>5.662681179918979</v>
+        <v>63.90097056987999</v>
       </c>
       <c r="AL55" t="n">
-        <v>0.686974309134137</v>
+        <v>1.48477810910068</v>
       </c>
       <c r="AM55" t="n">
-        <v>4.879258489269986</v>
+        <v>62.20991919277882</v>
       </c>
       <c r="AN55" t="n">
-        <v>6.162190332468593</v>
+        <v>64.99108767951434</v>
       </c>
       <c r="AO55" t="n">
-        <v>178.4642013566757</v>
+        <v>15.65491672489611</v>
       </c>
       <c r="AP55" t="n">
-        <v>23.12453841831484</v>
+        <v>0.3681157899251804</v>
       </c>
       <c r="AQ55" t="n">
-        <v>162.2799598920205</v>
+        <v>15.38672509885086</v>
       </c>
       <c r="AR55" t="n">
-        <v>204.9491745926369</v>
+        <v>16.07460695940074</v>
       </c>
       <c r="AS55" t="n">
-        <v>9.321341673533121</v>
+        <v>59.29124553998312</v>
       </c>
       <c r="AT55" t="n">
-        <v>1.077491522813341</v>
+        <v>0.7887952660340783</v>
       </c>
       <c r="AU55" t="n">
-        <v>8.084418058395386</v>
+        <v>58.54555773735046</v>
       </c>
       <c r="AV55" t="n">
-        <v>10.05600571632385</v>
+        <v>60.11703562736511</v>
       </c>
       <c r="AW55" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX55" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY55" t="n">
-        <v>4.823107294368561</v>
+        <v>3.926616133732436</v>
       </c>
       <c r="AZ55" t="n">
-        <v>6.982717448399336</v>
+        <v>4.632303340050877</v>
       </c>
       <c r="BA55" t="n">
         <v>10.18951102937502</v>
@@ -29181,10 +29181,10 @@
         <v>98.1869348859516</v>
       </c>
       <c r="BC55" t="n">
-        <v>17.51450102386532</v>
+        <v>1.53637565922104</v>
       </c>
       <c r="BD55" t="n">
-        <v>94.2327549113368</v>
+        <v>34.91906978855817</v>
       </c>
       <c r="BE55" t="n">
         <v>3</v>
@@ -29231,136 +29231,136 @@
         </is>
       </c>
       <c r="I56" t="n">
-        <v>0.9045575585741988</v>
+        <v>0.8297052480181289</v>
       </c>
       <c r="J56" t="n">
         <v>0</v>
       </c>
       <c r="K56" t="n">
-        <v>0.9045575585741988</v>
+        <v>0.8297052480181289</v>
       </c>
       <c r="L56" t="n">
-        <v>0.9045575585741988</v>
+        <v>0.8297052480181289</v>
       </c>
       <c r="M56" t="n">
-        <v>0.7456976377342096</v>
+        <v>0.8295355941953315</v>
       </c>
       <c r="N56" t="n">
         <v>0</v>
       </c>
       <c r="O56" t="n">
-        <v>0.7456976377342096</v>
+        <v>0.8295355941953315</v>
       </c>
       <c r="P56" t="n">
-        <v>0.7456976377342096</v>
+        <v>0.8295355941953315</v>
       </c>
       <c r="Q56" t="n">
-        <v>0.8870791824205587</v>
+        <v>0.8832205855459415</v>
       </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
       <c r="S56" t="n">
-        <v>0.8870791824205587</v>
+        <v>0.8832205855459414</v>
       </c>
       <c r="T56" t="n">
-        <v>0.8870791824205587</v>
+        <v>0.8832205855459414</v>
       </c>
       <c r="U56" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="V56" t="n">
         <v>0</v>
       </c>
       <c r="W56" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="X56" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="Y56" t="n">
-        <v>1.256413232551429</v>
+        <v>2.170604326501742</v>
       </c>
       <c r="Z56" t="n">
-        <v>0.08557543818342471</v>
+        <v>0.747060109868215</v>
       </c>
       <c r="AA56" t="n">
-        <v>1.159636200062811</v>
+        <v>1.717446163850702</v>
       </c>
       <c r="AB56" t="n">
-        <v>1.322087873500479</v>
+        <v>3.03285987229119</v>
       </c>
       <c r="AC56" t="n">
-        <v>4.036828275496531</v>
+        <v>60.91332641565706</v>
       </c>
       <c r="AD56" t="n">
-        <v>0.477536103150557</v>
+        <v>0.984809524561593</v>
       </c>
       <c r="AE56" t="n">
-        <v>3.487645795207919</v>
+        <v>60.31156338191199</v>
       </c>
       <c r="AF56" t="n">
-        <v>4.354311033686432</v>
+        <v>62.04982790481406</v>
       </c>
       <c r="AG56" t="n">
-        <v>0.3306661775178988</v>
+        <v>0.1782652168703022</v>
       </c>
       <c r="AH56" t="n">
-        <v>0.02295517200809089</v>
+        <v>0.009965861787121668</v>
       </c>
       <c r="AI56" t="n">
-        <v>0.3064756710736252</v>
+        <v>0.1693475192803225</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0.3521451650925313</v>
+        <v>0.1890228277206696</v>
       </c>
       <c r="AK56" t="n">
-        <v>5.623907685565858</v>
+        <v>63.26219595902911</v>
       </c>
       <c r="AL56" t="n">
-        <v>0.5845208049174803</v>
+        <v>0.9414420756640458</v>
       </c>
       <c r="AM56" t="n">
-        <v>4.953757666344354</v>
+        <v>62.19835706504301</v>
       </c>
       <c r="AN56" t="n">
-        <v>6.028544072279443</v>
+        <v>63.98776015178731</v>
       </c>
       <c r="AO56" t="n">
-        <v>179.1801529681308</v>
+        <v>15.80957932906928</v>
       </c>
       <c r="AP56" t="n">
-        <v>19.74479542964937</v>
+        <v>0.2369355231746624</v>
       </c>
       <c r="AQ56" t="n">
-        <v>165.8775299658532</v>
+        <v>15.62798881579648</v>
       </c>
       <c r="AR56" t="n">
-        <v>201.8669598624016</v>
+        <v>16.07759508750793</v>
       </c>
       <c r="AS56" t="n">
-        <v>9.444903294245401</v>
+        <v>58.29159593582153</v>
       </c>
       <c r="AT56" t="n">
-        <v>0.9514204125006295</v>
+        <v>1.300752034568336</v>
       </c>
       <c r="AU56" t="n">
-        <v>8.348035335540771</v>
+        <v>56.87005281448364</v>
       </c>
       <c r="AV56" t="n">
-        <v>10.04682850837708</v>
+        <v>59.42232847213745</v>
       </c>
       <c r="AW56" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX56" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY56" t="n">
-        <v>5.170931904528223</v>
+        <v>5.791645736798458</v>
       </c>
       <c r="AZ56" t="n">
-        <v>9.866175606361049</v>
+        <v>8.951380806422364</v>
       </c>
       <c r="BA56" t="n">
         <v>10.42768617105556</v>
@@ -29369,10 +29369,10 @@
         <v>95.90044595903659</v>
       </c>
       <c r="BC56" t="n">
-        <v>17.18311713920645</v>
+        <v>1.51611575854214</v>
       </c>
       <c r="BD56" t="n">
-        <v>94.13568140447639</v>
+        <v>34.03347051581883</v>
       </c>
       <c r="BE56" t="n">
         <v>3</v>
@@ -29419,136 +29419,136 @@
         </is>
       </c>
       <c r="I57" t="n">
-        <v>0.8729381786881008</v>
+        <v>0.8768088256656802</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
       </c>
       <c r="K57" t="n">
-        <v>0.8729381786881008</v>
+        <v>0.8768088256656802</v>
       </c>
       <c r="L57" t="n">
-        <v>0.8729381786881008</v>
+        <v>0.8768088256656802</v>
       </c>
       <c r="M57" t="n">
-        <v>0.8975638762461614</v>
+        <v>0.8870875723134087</v>
       </c>
       <c r="N57" t="n">
         <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>0.8975638762461614</v>
+        <v>0.8870875723134087</v>
       </c>
       <c r="P57" t="n">
-        <v>0.8975638762461614</v>
+        <v>0.8870875723134087</v>
       </c>
       <c r="Q57" t="n">
-        <v>0.9344103520410755</v>
+        <v>0.9362675415983444</v>
       </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
       <c r="S57" t="n">
-        <v>0.9344103520410754</v>
+        <v>0.9362675415983444</v>
       </c>
       <c r="T57" t="n">
-        <v>0.9344103520410754</v>
+        <v>0.9362675415983444</v>
       </c>
       <c r="U57" t="n">
-        <v>0.7952145538510432</v>
+        <v>0.808555114657571</v>
       </c>
       <c r="V57" t="n">
         <v>0</v>
       </c>
       <c r="W57" t="n">
-        <v>0.7952145538510431</v>
+        <v>0.808555114657571</v>
       </c>
       <c r="X57" t="n">
-        <v>0.7952145538510431</v>
+        <v>0.808555114657571</v>
       </c>
       <c r="Y57" t="n">
-        <v>1.259792308032281</v>
+        <v>3.261816277914791</v>
       </c>
       <c r="Z57" t="n">
-        <v>0.06323711663199527</v>
+        <v>0.08147622200309464</v>
       </c>
       <c r="AA57" t="n">
-        <v>1.213023071072548</v>
+        <v>3.185828581927783</v>
       </c>
       <c r="AB57" t="n">
-        <v>1.331740408425843</v>
+        <v>3.347849456626334</v>
       </c>
       <c r="AC57" t="n">
-        <v>4.014308767082148</v>
+        <v>61.34059028473661</v>
       </c>
       <c r="AD57" t="n">
-        <v>0.2993357269720452</v>
+        <v>0.7313447036459689</v>
       </c>
       <c r="AE57" t="n">
-        <v>3.805790138599205</v>
+        <v>60.6550611361443</v>
       </c>
       <c r="AF57" t="n">
-        <v>4.357297768676443</v>
+        <v>62.11044081686062</v>
       </c>
       <c r="AG57" t="n">
-        <v>0.3237033931710981</v>
+        <v>0.1932813108429531</v>
       </c>
       <c r="AH57" t="n">
-        <v>0.01117948503257372</v>
+        <v>0.002995599576510595</v>
       </c>
       <c r="AI57" t="n">
-        <v>0.3160019493724937</v>
+        <v>0.1901159879444861</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0.3365261108437076</v>
+        <v>0.1960719313287937</v>
       </c>
       <c r="AK57" t="n">
-        <v>5.597804468285527</v>
+        <v>64.79568787349434</v>
       </c>
       <c r="AL57" t="n">
-        <v>0.3736918257033194</v>
+        <v>0.6929596913562658</v>
       </c>
       <c r="AM57" t="n">
-        <v>5.334815159044246</v>
+        <v>64.10048794459013</v>
       </c>
       <c r="AN57" t="n">
-        <v>6.025564287945993</v>
+        <v>65.48638538673288</v>
       </c>
       <c r="AO57" t="n">
-        <v>179.1555669158573</v>
+        <v>15.43430277843191</v>
       </c>
       <c r="AP57" t="n">
-        <v>11.55299788837336</v>
+        <v>0.1650893196644596</v>
       </c>
       <c r="AQ57" t="n">
-        <v>165.959560335366</v>
+        <v>15.2703496168624</v>
       </c>
       <c r="AR57" t="n">
-        <v>187.4479190351469</v>
+        <v>15.60050527016927</v>
       </c>
       <c r="AS57" t="n">
-        <v>9.392655769983929</v>
+        <v>59.91524775822958</v>
       </c>
       <c r="AT57" t="n">
-        <v>0.5050904829458298</v>
+        <v>1.241040658438063</v>
       </c>
       <c r="AU57" t="n">
-        <v>9.089143037796021</v>
+        <v>58.88414597511292</v>
       </c>
       <c r="AV57" t="n">
-        <v>9.975719928741457</v>
+        <v>61.29265928268433</v>
       </c>
       <c r="AW57" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX57" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY57" t="n">
-        <v>0.1112136787719119</v>
+        <v>0.1334143615863571</v>
       </c>
       <c r="AZ57" t="n">
-        <v>1.112128430494858</v>
+        <v>0.2546603051363033</v>
       </c>
       <c r="BA57" t="n">
         <v>9.989141990029484</v>
@@ -29557,10 +29557,10 @@
         <v>100.1151881156658</v>
       </c>
       <c r="BC57" t="n">
-        <v>17.93503056565607</v>
+        <v>1.54510795760411</v>
       </c>
       <c r="BD57" t="n">
-        <v>94.40863611840969</v>
+        <v>35.27886318444101</v>
       </c>
       <c r="BE57" t="n">
         <v>3</v>
@@ -29607,136 +29607,136 @@
         </is>
       </c>
       <c r="I58" t="n">
-        <v>0.8707140569750392</v>
+        <v>0.8964423867891718</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
       </c>
       <c r="K58" t="n">
-        <v>0.8707140569750392</v>
+        <v>0.8964423867891718</v>
       </c>
       <c r="L58" t="n">
-        <v>0.8707140569750392</v>
+        <v>0.8964423867891718</v>
       </c>
       <c r="M58" t="n">
-        <v>0.8522574775721816</v>
+        <v>0.8518205142742233</v>
       </c>
       <c r="N58" t="n">
         <v>0</v>
       </c>
       <c r="O58" t="n">
-        <v>0.8522574775721816</v>
+        <v>0.8518205142742233</v>
       </c>
       <c r="P58" t="n">
-        <v>0.8522574775721816</v>
+        <v>0.8518205142742233</v>
       </c>
       <c r="Q58" t="n">
-        <v>0.9083748763111515</v>
+        <v>0.9345543815455292</v>
       </c>
       <c r="R58" t="n">
         <v>0</v>
       </c>
       <c r="S58" t="n">
-        <v>0.9083748763111515</v>
+        <v>0.9345543815455292</v>
       </c>
       <c r="T58" t="n">
-        <v>0.9083748763111515</v>
+        <v>0.9345543815455292</v>
       </c>
       <c r="U58" t="n">
-        <v>0.7699517482344933</v>
+        <v>0.8062458515669091</v>
       </c>
       <c r="V58" t="n">
         <v>0</v>
       </c>
       <c r="W58" t="n">
-        <v>0.7699517482344933</v>
+        <v>0.8062458515669091</v>
       </c>
       <c r="X58" t="n">
-        <v>0.7699517482344933</v>
+        <v>0.8062458515669091</v>
       </c>
       <c r="Y58" t="n">
-        <v>1.280953927299967</v>
+        <v>3.157242657027608</v>
       </c>
       <c r="Z58" t="n">
-        <v>0.09617042301070693</v>
+        <v>0.1770414457765514</v>
       </c>
       <c r="AA58" t="n">
-        <v>1.180629424121128</v>
+        <v>2.97798864938334</v>
       </c>
       <c r="AB58" t="n">
-        <v>1.3723471843161</v>
+        <v>3.331985312055928</v>
       </c>
       <c r="AC58" t="n">
-        <v>4.081473767871786</v>
+        <v>61.10961964698555</v>
       </c>
       <c r="AD58" t="n">
-        <v>0.5649141756957149</v>
+        <v>0.3205802739772741</v>
       </c>
       <c r="AE58" t="n">
-        <v>3.429347692751862</v>
+        <v>60.90852873614045</v>
       </c>
       <c r="AF58" t="n">
-        <v>4.420830131331683</v>
+        <v>61.4793184903581</v>
       </c>
       <c r="AG58" t="n">
-        <v>0.3336857048368647</v>
+        <v>0.1962975493976652</v>
       </c>
       <c r="AH58" t="n">
-        <v>0.02242060347165801</v>
+        <v>0.001437131434905969</v>
       </c>
       <c r="AI58" t="n">
-        <v>0.3083778614886084</v>
+        <v>0.1949709096393289</v>
       </c>
       <c r="AJ58" t="n">
-        <v>0.3510638469576286</v>
+        <v>0.1978242156585921</v>
       </c>
       <c r="AK58" t="n">
-        <v>5.696113400008618</v>
+        <v>64.46315985341083</v>
       </c>
       <c r="AL58" t="n">
-        <v>0.6739584456883166</v>
+        <v>0.1926938449485868</v>
       </c>
       <c r="AM58" t="n">
-        <v>4.918354978361599</v>
+        <v>64.26810696144261</v>
       </c>
       <c r="AN58" t="n">
-        <v>6.108206069912269</v>
+        <v>64.6534046626365</v>
       </c>
       <c r="AO58" t="n">
-        <v>177.33409022152</v>
+        <v>15.51282872118186</v>
       </c>
       <c r="AP58" t="n">
-        <v>22.51320069787497</v>
+        <v>0.04637647583024194</v>
       </c>
       <c r="AQ58" t="n">
-        <v>163.7141885120393</v>
+        <v>15.46708955573232</v>
       </c>
       <c r="AR58" t="n">
-        <v>203.3200133783592</v>
+        <v>15.55981726052622</v>
       </c>
       <c r="AS58" t="n">
-        <v>9.463728745778402</v>
+        <v>59.42715207735697</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.139183168922785</v>
+        <v>0.7286155769868764</v>
       </c>
       <c r="AU58" t="n">
-        <v>8.155663728713989</v>
+        <v>58.92950129508972</v>
       </c>
       <c r="AV58" t="n">
-        <v>10.2380223274231</v>
+        <v>60.26346230506897</v>
       </c>
       <c r="AW58" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX58" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY58" t="n">
-        <v>2.89441494176859</v>
+        <v>0.3161478619218554</v>
       </c>
       <c r="AZ58" t="n">
-        <v>4.253651765545279</v>
+        <v>0.5395366570970905</v>
       </c>
       <c r="BA58" t="n">
         <v>10.11051489610476</v>
@@ -29745,10 +29745,10 @@
         <v>98.94876418675778</v>
       </c>
       <c r="BC58" t="n">
-        <v>17.53957063945782</v>
+        <v>1.534326281162835</v>
       </c>
       <c r="BD58" t="n">
-        <v>94.24337085276005</v>
+        <v>34.85198083753544</v>
       </c>
       <c r="BE58" t="n">
         <v>3</v>
@@ -29795,136 +29795,136 @@
         </is>
       </c>
       <c r="I59" t="n">
-        <v>0.8888511745802176</v>
+        <v>0.9007242709230804</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
       </c>
       <c r="K59" t="n">
-        <v>0.8888511745802176</v>
+        <v>0.9007242709230804</v>
       </c>
       <c r="L59" t="n">
-        <v>0.8888511745802176</v>
+        <v>0.9007242709230804</v>
       </c>
       <c r="M59" t="n">
-        <v>0.8423088650259937</v>
+        <v>0.8634411034374985</v>
       </c>
       <c r="N59" t="n">
         <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>0.8423088650259938</v>
+        <v>0.8634411034374985</v>
       </c>
       <c r="P59" t="n">
-        <v>0.8423088650259938</v>
+        <v>0.8634411034374985</v>
       </c>
       <c r="Q59" t="n">
-        <v>0.920816621002182</v>
+        <v>0.9232057676193612</v>
       </c>
       <c r="R59" t="n">
         <v>0</v>
       </c>
       <c r="S59" t="n">
-        <v>0.920816621002182</v>
+        <v>0.9232057676193612</v>
       </c>
       <c r="T59" t="n">
-        <v>0.920816621002182</v>
+        <v>0.9232057676193612</v>
       </c>
       <c r="U59" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="V59" t="n">
         <v>0</v>
       </c>
       <c r="W59" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="X59" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="Y59" t="n">
-        <v>1.215081399569758</v>
+        <v>2.823390071484189</v>
       </c>
       <c r="Z59" t="n">
-        <v>0.04509922180845374</v>
+        <v>0.5369609153102619</v>
       </c>
       <c r="AA59" t="n">
-        <v>1.168852561401643</v>
+        <v>2.20589367469918</v>
       </c>
       <c r="AB59" t="n">
-        <v>1.258959024065018</v>
+        <v>3.180622025290056</v>
       </c>
       <c r="AC59" t="n">
-        <v>3.864816064655695</v>
+        <v>61.4326239843324</v>
       </c>
       <c r="AD59" t="n">
-        <v>0.4834258030646357</v>
+        <v>0.3006996045912227</v>
       </c>
       <c r="AE59" t="n">
-        <v>3.465931490374868</v>
+        <v>61.13945347229586</v>
       </c>
       <c r="AF59" t="n">
-        <v>4.402442960211824</v>
+        <v>61.74032578312481</v>
       </c>
       <c r="AG59" t="n">
-        <v>0.3269186136759274</v>
+        <v>0.1977847899641814</v>
       </c>
       <c r="AH59" t="n">
-        <v>0.02090250728227047</v>
+        <v>0.001400571269237281</v>
       </c>
       <c r="AI59" t="n">
-        <v>0.3117338686999836</v>
+        <v>0.1966948734941278</v>
       </c>
       <c r="AJ59" t="n">
-        <v>0.3507585229217292</v>
+        <v>0.199364475915297</v>
       </c>
       <c r="AK59" t="n">
-        <v>5.40681607790138</v>
+        <v>64.45379884578078</v>
       </c>
       <c r="AL59" t="n">
-        <v>0.5474279371725285</v>
+        <v>0.6504588154688254</v>
       </c>
       <c r="AM59" t="n">
-        <v>4.946517920476494</v>
+        <v>63.82068124576985</v>
       </c>
       <c r="AN59" t="n">
-        <v>6.01216050719857</v>
+        <v>65.12031228433017</v>
       </c>
       <c r="AO59" t="n">
-        <v>186.1806981698334</v>
+        <v>15.51604202231935</v>
       </c>
       <c r="AP59" t="n">
-        <v>18.22711485469044</v>
+        <v>0.1564722947781896</v>
       </c>
       <c r="AQ59" t="n">
-        <v>166.3295580353627</v>
+        <v>15.35619171532488</v>
       </c>
       <c r="AR59" t="n">
-        <v>202.1624132524462</v>
+        <v>15.66890199979308</v>
       </c>
       <c r="AS59" t="n">
-        <v>8.934955755869547</v>
+        <v>59.32744558652242</v>
       </c>
       <c r="AT59" t="n">
-        <v>0.8222815666111919</v>
+        <v>0.8598111715155307</v>
       </c>
       <c r="AU59" t="n">
-        <v>8.191219329833984</v>
+        <v>58.35378503799439</v>
       </c>
       <c r="AV59" t="n">
-        <v>9.817988395690918</v>
+        <v>59.98239517211914</v>
       </c>
       <c r="AW59" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX59" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY59" t="n">
-        <v>1.564388177626981</v>
+        <v>1.526643018680312</v>
       </c>
       <c r="AZ59" t="n">
-        <v>4.614860405212791</v>
+        <v>4.183858364223433</v>
       </c>
       <c r="BA59" t="n">
         <v>10.23204564484659</v>
@@ -29933,10 +29933,10 @@
         <v>97.74566249718235</v>
       </c>
       <c r="BC59" t="n">
-        <v>18.19584320009401</v>
+        <v>1.516416419636876</v>
       </c>
       <c r="BD59" t="n">
-        <v>94.46848490278815</v>
+        <v>34.05968387841379</v>
       </c>
       <c r="BE59" t="n">
         <v>3</v>
@@ -29983,136 +29983,136 @@
         </is>
       </c>
       <c r="I60" t="n">
-        <v>0.8713330186365799</v>
+        <v>0.8894432429992767</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
       </c>
       <c r="K60" t="n">
-        <v>0.8713330186365799</v>
+        <v>0.8894432429992767</v>
       </c>
       <c r="L60" t="n">
-        <v>0.8713330186365799</v>
+        <v>0.8894432429992767</v>
       </c>
       <c r="M60" t="n">
-        <v>0.8834321987481178</v>
+        <v>0.8632367360036634</v>
       </c>
       <c r="N60" t="n">
         <v>0</v>
       </c>
       <c r="O60" t="n">
-        <v>0.8834321987481178</v>
+        <v>0.8632367360036634</v>
       </c>
       <c r="P60" t="n">
-        <v>0.8834321987481178</v>
+        <v>0.8632367360036634</v>
       </c>
       <c r="Q60" t="n">
-        <v>0.9344102707423176</v>
+        <v>0.9324929045585608</v>
       </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>0.9344102707423176</v>
+        <v>0.9324929045585608</v>
       </c>
       <c r="T60" t="n">
-        <v>0.9344102707423176</v>
+        <v>0.9324929045585608</v>
       </c>
       <c r="U60" t="n">
-        <v>0.7969907346365336</v>
+        <v>0.8003892058753374</v>
       </c>
       <c r="V60" t="n">
         <v>0</v>
       </c>
       <c r="W60" t="n">
-        <v>0.7969907346365336</v>
+        <v>0.8003892058753374</v>
       </c>
       <c r="X60" t="n">
-        <v>0.7969907346365336</v>
+        <v>0.8003892058753374</v>
       </c>
       <c r="Y60" t="n">
-        <v>1.264671748600471</v>
+        <v>3.130138997188492</v>
       </c>
       <c r="Z60" t="n">
-        <v>0.07881859441977264</v>
+        <v>0.09385659695440438</v>
       </c>
       <c r="AA60" t="n">
-        <v>1.191541687975072</v>
+        <v>3.022330383129818</v>
       </c>
       <c r="AB60" t="n">
-        <v>1.348155501199723</v>
+        <v>3.193636939760332</v>
       </c>
       <c r="AC60" t="n">
-        <v>4.003888853002715</v>
+        <v>60.90456090561772</v>
       </c>
       <c r="AD60" t="n">
-        <v>0.3544504618834989</v>
+        <v>0.422953370826831</v>
       </c>
       <c r="AE60" t="n">
-        <v>3.659971907216525</v>
+        <v>60.52263838673807</v>
       </c>
       <c r="AF60" t="n">
-        <v>4.368008666259187</v>
+        <v>61.35913351927668</v>
       </c>
       <c r="AG60" t="n">
-        <v>0.3248493550269911</v>
+        <v>0.1961008959773403</v>
       </c>
       <c r="AH60" t="n">
-        <v>0.01651603235086498</v>
+        <v>0.002117966700986215</v>
       </c>
       <c r="AI60" t="n">
-        <v>0.3118361048262772</v>
+        <v>0.1940091337358802</v>
       </c>
       <c r="AJ60" t="n">
-        <v>0.3434295385930629</v>
+        <v>0.1982441289060097</v>
       </c>
       <c r="AK60" t="n">
-        <v>5.593409956630178</v>
+        <v>64.23080079878356</v>
       </c>
       <c r="AL60" t="n">
-        <v>0.4492126552509194</v>
+        <v>0.4574958216980837</v>
       </c>
       <c r="AM60" t="n">
-        <v>5.163349700017873</v>
+        <v>63.89109718914928</v>
       </c>
       <c r="AN60" t="n">
-        <v>6.059593706051974</v>
+        <v>64.75101458794302</v>
       </c>
       <c r="AO60" t="n">
-        <v>179.5480752440816</v>
+        <v>15.56937934229981</v>
       </c>
       <c r="AP60" t="n">
-        <v>14.3266812401807</v>
+        <v>0.1105031992553643</v>
       </c>
       <c r="AQ60" t="n">
-        <v>165.0275659573113</v>
+        <v>15.44377345071293</v>
       </c>
       <c r="AR60" t="n">
-        <v>193.6727237352408</v>
+        <v>15.65163291905138</v>
       </c>
       <c r="AS60" t="n">
-        <v>9.297200759251913</v>
+        <v>59.40397461255392</v>
       </c>
       <c r="AT60" t="n">
-        <v>0.8016723146283042</v>
+        <v>0.6606717077982324</v>
       </c>
       <c r="AU60" t="n">
-        <v>8.495866537094116</v>
+        <v>58.71746230125427</v>
       </c>
       <c r="AV60" t="n">
-        <v>10.09921073913574</v>
+        <v>60.03535008430481</v>
       </c>
       <c r="AW60" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX60" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY60" t="n">
-        <v>0.1112223696369393</v>
+        <v>0.536034442320914</v>
       </c>
       <c r="AZ60" t="n">
-        <v>0.8912537790574629</v>
+        <v>1.262026816875109</v>
       </c>
       <c r="BA60" t="n">
         <v>10.50355009694286</v>
@@ -30121,10 +30121,10 @@
         <v>95.21822548071593</v>
       </c>
       <c r="BC60" t="n">
-        <v>17.09403711953927</v>
+        <v>1.482296861404164</v>
       </c>
       <c r="BD60" t="n">
-        <v>94.12569397466561</v>
+        <v>32.5435855640978</v>
       </c>
       <c r="BE60" t="n">
         <v>3</v>
@@ -30171,136 +30171,136 @@
         </is>
       </c>
       <c r="I61" t="n">
-        <v>0.8626638400446858</v>
+        <v>0.8821708147587138</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
       </c>
       <c r="K61" t="n">
-        <v>0.8626638400446858</v>
+        <v>0.8821708147587138</v>
       </c>
       <c r="L61" t="n">
-        <v>0.8626638400446858</v>
+        <v>0.8821708147587138</v>
       </c>
       <c r="M61" t="n">
-        <v>0.8994504233176549</v>
+        <v>0.8695893830757188</v>
       </c>
       <c r="N61" t="n">
         <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>0.8994504233176549</v>
+        <v>0.8695893830757189</v>
       </c>
       <c r="P61" t="n">
-        <v>0.8994504233176549</v>
+        <v>0.8695893830757189</v>
       </c>
       <c r="Q61" t="n">
-        <v>0.933442221253304</v>
+        <v>0.9286825537818112</v>
       </c>
       <c r="R61" t="n">
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>0.933442221253304</v>
+        <v>0.9286825537818112</v>
       </c>
       <c r="T61" t="n">
-        <v>0.933442221253304</v>
+        <v>0.9286825537818112</v>
       </c>
       <c r="U61" t="n">
-        <v>0.8022050375687061</v>
+        <v>0.8024096003660924</v>
       </c>
       <c r="V61" t="n">
         <v>0</v>
       </c>
       <c r="W61" t="n">
-        <v>0.8022050375687061</v>
+        <v>0.8024096003660925</v>
       </c>
       <c r="X61" t="n">
-        <v>0.8022050375687061</v>
+        <v>0.8024096003660925</v>
       </c>
       <c r="Y61" t="n">
-        <v>1.291705223267642</v>
+        <v>2.718886951404886</v>
       </c>
       <c r="Z61" t="n">
-        <v>0.08089882716378545</v>
+        <v>0.4815885544145597</v>
       </c>
       <c r="AA61" t="n">
-        <v>1.200417616807926</v>
+        <v>2.223207268669132</v>
       </c>
       <c r="AB61" t="n">
-        <v>1.354511483099574</v>
+        <v>3.185024238555672</v>
       </c>
       <c r="AC61" t="n">
-        <v>4.141069375116669</v>
+        <v>61.28982167991393</v>
       </c>
       <c r="AD61" t="n">
-        <v>0.4666293863881644</v>
+        <v>0.6437673253075923</v>
       </c>
       <c r="AE61" t="n">
-        <v>3.633441634975684</v>
+        <v>60.79805563854937</v>
       </c>
       <c r="AF61" t="n">
-        <v>4.551339444554627</v>
+        <v>62.01846860723605</v>
       </c>
       <c r="AG61" t="n">
-        <v>0.3287270493738142</v>
+        <v>0.1953174385555</v>
       </c>
       <c r="AH61" t="n">
-        <v>0.01627368551985348</v>
+        <v>0.001379213896457041</v>
       </c>
       <c r="AI61" t="n">
-        <v>0.3113038506020837</v>
+        <v>0.1937291132495615</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0.3435342987512444</v>
+        <v>0.1962123385603635</v>
       </c>
       <c r="AK61" t="n">
-        <v>5.761501647758126</v>
+        <v>64.20402606987432</v>
       </c>
       <c r="AL61" t="n">
-        <v>0.5632070078141208</v>
+        <v>0.2213109058245358</v>
       </c>
       <c r="AM61" t="n">
-        <v>5.145163102385694</v>
+        <v>63.99758247950657</v>
       </c>
       <c r="AN61" t="n">
-        <v>6.249385226405446</v>
+        <v>64.43768673976176</v>
       </c>
       <c r="AO61" t="n">
-        <v>174.7178585323763</v>
+        <v>15.57547053551403</v>
       </c>
       <c r="AP61" t="n">
-        <v>17.6951551359616</v>
+        <v>0.05365524225775704</v>
       </c>
       <c r="AQ61" t="n">
-        <v>160.015739752242</v>
+        <v>15.51886870238845</v>
       </c>
       <c r="AR61" t="n">
-        <v>194.3572983208876</v>
+        <v>15.6255902372597</v>
       </c>
       <c r="AS61" t="n">
-        <v>9.579611221949259</v>
+        <v>59.28412262598673</v>
       </c>
       <c r="AT61" t="n">
-        <v>0.8504041861205344</v>
+        <v>0.5010737911191697</v>
       </c>
       <c r="AU61" t="n">
-        <v>8.618870258331299</v>
+        <v>58.94184541702271</v>
       </c>
       <c r="AV61" t="n">
-        <v>10.23582220077515</v>
+        <v>59.85925340652466</v>
       </c>
       <c r="AW61" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX61" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY61" t="n">
-        <v>0.2147071912094278</v>
+        <v>0.942463913868169</v>
       </c>
       <c r="AZ61" t="n">
-        <v>0.2428359197714576</v>
+        <v>1.012786003052116</v>
       </c>
       <c r="BA61" t="n">
         <v>10.53165151035015</v>
@@ -30309,10 +30309,10 @@
         <v>94.96451680249108</v>
       </c>
       <c r="BC61" t="n">
-        <v>16.58978730550185</v>
+        <v>1.478920045940277</v>
       </c>
       <c r="BD61" t="n">
-        <v>93.93299535263155</v>
+        <v>32.39156241545775</v>
       </c>
       <c r="BE61" t="n">
         <v>3</v>
@@ -30359,136 +30359,136 @@
         </is>
       </c>
       <c r="I62" t="n">
-        <v>0.8366387179945584</v>
+        <v>0.8662210580690296</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
       </c>
       <c r="K62" t="n">
-        <v>0.8366387179945585</v>
+        <v>0.8662210580690296</v>
       </c>
       <c r="L62" t="n">
-        <v>0.8366387179945585</v>
+        <v>0.8662210580690296</v>
       </c>
       <c r="M62" t="n">
-        <v>0.8299938487051532</v>
+        <v>0.8412129116577401</v>
       </c>
       <c r="N62" t="n">
         <v>0</v>
       </c>
       <c r="O62" t="n">
-        <v>0.8299938487051532</v>
+        <v>0.8412129116577401</v>
       </c>
       <c r="P62" t="n">
-        <v>0.8299938487051532</v>
+        <v>0.8412129116577401</v>
       </c>
       <c r="Q62" t="n">
-        <v>0.9002848662126398</v>
+        <v>0.9235417287411419</v>
       </c>
       <c r="R62" t="n">
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>0.9002848662126398</v>
+        <v>0.923541728741142</v>
       </c>
       <c r="T62" t="n">
-        <v>0.9002848662126398</v>
+        <v>0.923541728741142</v>
       </c>
       <c r="U62" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416777</v>
       </c>
       <c r="V62" t="n">
         <v>0</v>
       </c>
       <c r="W62" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416778</v>
       </c>
       <c r="X62" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416778</v>
       </c>
       <c r="Y62" t="n">
-        <v>1.273206406041578</v>
+        <v>3.084528051404671</v>
       </c>
       <c r="Z62" t="n">
-        <v>0.04377367211860447</v>
+        <v>0.1277287731654614</v>
       </c>
       <c r="AA62" t="n">
-        <v>1.242350834976364</v>
+        <v>2.955306515659357</v>
       </c>
       <c r="AB62" t="n">
-        <v>1.323305284309009</v>
+        <v>3.210709798797478</v>
       </c>
       <c r="AC62" t="n">
-        <v>4.226664143777406</v>
+        <v>62.07660985541878</v>
       </c>
       <c r="AD62" t="n">
-        <v>0.3308915886694174</v>
+        <v>0.2054515466693488</v>
       </c>
       <c r="AE62" t="n">
-        <v>3.878452881949067</v>
+        <v>61.95215227952736</v>
       </c>
       <c r="AF62" t="n">
-        <v>4.536971578292365</v>
+        <v>62.31374739637946</v>
       </c>
       <c r="AG62" t="n">
-        <v>0.3236632711008839</v>
+        <v>0.1970441405613468</v>
       </c>
       <c r="AH62" t="n">
-        <v>0.005544551874649899</v>
+        <v>0.0004664107564050874</v>
       </c>
       <c r="AI62" t="n">
-        <v>0.319656326537808</v>
+        <v>0.1966932481892915</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0.329991133737375</v>
+        <v>0.1975734156624102</v>
       </c>
       <c r="AK62" t="n">
-        <v>5.823533820919867</v>
+        <v>65.3581820473848</v>
       </c>
       <c r="AL62" t="n">
-        <v>0.3751709323693725</v>
+        <v>0.2414832094330966</v>
       </c>
       <c r="AM62" t="n">
-        <v>5.44046004346324</v>
+        <v>65.11592965419817</v>
       </c>
       <c r="AN62" t="n">
-        <v>6.190267996338749</v>
+        <v>65.59888865179904</v>
       </c>
       <c r="AO62" t="n">
-        <v>172.1961559852246</v>
+        <v>15.30044242337567</v>
       </c>
       <c r="AP62" t="n">
-        <v>11.16301990987924</v>
+        <v>0.05653395056725858</v>
       </c>
       <c r="AQ62" t="n">
-        <v>161.5438944794398</v>
+        <v>15.24416069467322</v>
       </c>
       <c r="AR62" t="n">
-        <v>183.8079853562216</v>
+        <v>15.3572252643947</v>
       </c>
       <c r="AS62" t="n">
-        <v>9.59859307607015</v>
+        <v>60.66661739349365</v>
       </c>
       <c r="AT62" t="n">
-        <v>0.5041514544200026</v>
+        <v>0.1368778697374766</v>
       </c>
       <c r="AU62" t="n">
-        <v>9.060518503189089</v>
+        <v>60.51085138320923</v>
       </c>
       <c r="AV62" t="n">
-        <v>10.06005048751831</v>
+        <v>60.76770091056824</v>
       </c>
       <c r="AW62" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX62" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY62" t="n">
-        <v>3.759239789119267</v>
+        <v>1.490807866174425</v>
       </c>
       <c r="AZ62" t="n">
-        <v>4.93796172305524</v>
+        <v>2.002068621107012</v>
       </c>
       <c r="BA62" t="n">
         <v>10.58551849793414</v>
@@ -30497,10 +30497,10 @@
         <v>94.4711289337143</v>
       </c>
       <c r="BC62" t="n">
-        <v>16.26714421394004</v>
+        <v>1.445412657524682</v>
       </c>
       <c r="BD62" t="n">
-        <v>93.83564705254454</v>
+        <v>30.81676615377022</v>
       </c>
       <c r="BE62" t="n">
         <v>3</v>
@@ -30547,136 +30547,136 @@
         </is>
       </c>
       <c r="I63" t="n">
-        <v>0.8179731363167645</v>
+        <v>0.8596283736711174</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
       </c>
       <c r="K63" t="n">
-        <v>0.8179731363167645</v>
+        <v>0.8596283736711174</v>
       </c>
       <c r="L63" t="n">
-        <v>0.8179731363167645</v>
+        <v>0.8596283736711174</v>
       </c>
       <c r="M63" t="n">
-        <v>0.8614344192967365</v>
+        <v>0.8906635781698</v>
       </c>
       <c r="N63" t="n">
         <v>0</v>
       </c>
       <c r="O63" t="n">
-        <v>0.8614344192967365</v>
+        <v>0.8906635781698</v>
       </c>
       <c r="P63" t="n">
-        <v>0.8614344192967365</v>
+        <v>0.8906635781698</v>
       </c>
       <c r="Q63" t="n">
-        <v>0.9021413829153112</v>
+        <v>0.9307901364833598</v>
       </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>0.9021413829153112</v>
+        <v>0.9307901364833598</v>
       </c>
       <c r="T63" t="n">
-        <v>0.9021413829153112</v>
+        <v>0.9307901364833598</v>
       </c>
       <c r="U63" t="n">
-        <v>0.7575501107005344</v>
+        <v>0.7837667125667425</v>
       </c>
       <c r="V63" t="n">
         <v>0</v>
       </c>
       <c r="W63" t="n">
-        <v>0.7575501107005344</v>
+        <v>0.7837667125667425</v>
       </c>
       <c r="X63" t="n">
-        <v>0.7575501107005344</v>
+        <v>0.7837667125667425</v>
       </c>
       <c r="Y63" t="n">
-        <v>1.292765069489127</v>
+        <v>3.20941831244666</v>
       </c>
       <c r="Z63" t="n">
-        <v>0.08274931856610483</v>
+        <v>0.1689051358635247</v>
       </c>
       <c r="AA63" t="n">
-        <v>1.198618190381196</v>
+        <v>3.05711818673773</v>
       </c>
       <c r="AB63" t="n">
-        <v>1.353970868677355</v>
+        <v>3.391078795179252</v>
       </c>
       <c r="AC63" t="n">
-        <v>4.181870787940707</v>
+        <v>62.6864378265089</v>
       </c>
       <c r="AD63" t="n">
-        <v>0.5492213155135708</v>
+        <v>0.8056310559747104</v>
       </c>
       <c r="AE63" t="n">
-        <v>3.54956285903109</v>
+        <v>61.99581863132657</v>
       </c>
       <c r="AF63" t="n">
-        <v>4.540262954215434</v>
+        <v>63.57149296024206</v>
       </c>
       <c r="AG63" t="n">
-        <v>0.3409352931716474</v>
+        <v>0.1993768602385599</v>
       </c>
       <c r="AH63" t="n">
-        <v>0.02572868243006786</v>
+        <v>0.004347084255734677</v>
       </c>
       <c r="AI63" t="n">
-        <v>0.3139827542239449</v>
+        <v>0.1947455072317404</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0.3652344819740217</v>
+        <v>0.203368862641407</v>
       </c>
       <c r="AK63" t="n">
-        <v>5.815571150601481</v>
+        <v>66.09523299919412</v>
       </c>
       <c r="AL63" t="n">
-        <v>0.6559206786690056</v>
+        <v>0.9784058391120121</v>
       </c>
       <c r="AM63" t="n">
-        <v>5.06216380363623</v>
+        <v>65.24768232529604</v>
       </c>
       <c r="AN63" t="n">
-        <v>6.25946830486681</v>
+        <v>67.16594061806272</v>
       </c>
       <c r="AO63" t="n">
-        <v>173.5216996228591</v>
+        <v>15.13188425750472</v>
       </c>
       <c r="AP63" t="n">
-        <v>20.87759822806558</v>
+        <v>0.2229433546002845</v>
       </c>
       <c r="AQ63" t="n">
-        <v>159.7579780414398</v>
+        <v>14.88849840853823</v>
       </c>
       <c r="AR63" t="n">
-        <v>197.5439829271594</v>
+        <v>15.32621488399301</v>
       </c>
       <c r="AS63" t="n">
-        <v>9.570940017700195</v>
+        <v>61.00344355901083</v>
       </c>
       <c r="AT63" t="n">
-        <v>1.006151841822825</v>
+        <v>0.6012515221676051</v>
       </c>
       <c r="AU63" t="n">
-        <v>8.409804105758667</v>
+        <v>60.31957316398621</v>
       </c>
       <c r="AV63" t="n">
-        <v>10.18562650680542</v>
+        <v>61.44903373718262</v>
       </c>
       <c r="AW63" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX63" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY63" t="n">
-        <v>3.560777518437165</v>
+        <v>0.7176594867116615</v>
       </c>
       <c r="AZ63" t="n">
-        <v>5.79584127122101</v>
+        <v>3.312618312228618</v>
       </c>
       <c r="BA63" t="n">
         <v>10.45574714262228</v>
@@ -30685,10 +30685,10 @@
         <v>95.65549920760122</v>
       </c>
       <c r="BC63" t="n">
-        <v>16.59582019877923</v>
+        <v>1.447231273968019</v>
       </c>
       <c r="BD63" t="n">
-        <v>93.92029606371094</v>
+        <v>30.90284035239043</v>
       </c>
       <c r="BE63" t="n">
         <v>3</v>
@@ -30735,136 +30735,136 @@
         </is>
       </c>
       <c r="I64" t="n">
-        <v>0.7070219511570386</v>
+        <v>0.7958074694235807</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
       </c>
       <c r="K64" t="n">
-        <v>0.7070219511570386</v>
+        <v>0.7958074694235807</v>
       </c>
       <c r="L64" t="n">
-        <v>0.7070219511570386</v>
+        <v>0.7958074694235807</v>
       </c>
       <c r="M64" t="n">
-        <v>0.6390600007387984</v>
+        <v>0.6532800973615224</v>
       </c>
       <c r="N64" t="n">
         <v>0</v>
       </c>
       <c r="O64" t="n">
-        <v>0.6390600007387984</v>
+        <v>0.6532800973615224</v>
       </c>
       <c r="P64" t="n">
-        <v>0.6390600007387984</v>
+        <v>0.6532800973615224</v>
       </c>
       <c r="Q64" t="n">
-        <v>0.7205195768217173</v>
+        <v>0.751252205640335</v>
       </c>
       <c r="R64" t="n">
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>0.7205195768217172</v>
+        <v>0.751252205640335</v>
       </c>
       <c r="T64" t="n">
-        <v>0.7205195768217172</v>
+        <v>0.751252205640335</v>
       </c>
       <c r="U64" t="n">
-        <v>0.5475915817275469</v>
+        <v>0.5839382459240198</v>
       </c>
       <c r="V64" t="n">
         <v>0</v>
       </c>
       <c r="W64" t="n">
-        <v>0.5475915817275469</v>
+        <v>0.5839382459240198</v>
       </c>
       <c r="X64" t="n">
-        <v>0.5475915817275469</v>
+        <v>0.5839382459240198</v>
       </c>
       <c r="Y64" t="n">
-        <v>1.246453375487286</v>
+        <v>3.079333340956071</v>
       </c>
       <c r="Z64" t="n">
-        <v>0.03696187889073316</v>
+        <v>0.2363891611088419</v>
       </c>
       <c r="AA64" t="n">
-        <v>1.205356446954251</v>
+        <v>2.811398706029628</v>
       </c>
       <c r="AB64" t="n">
-        <v>1.276974920521358</v>
+        <v>3.258446079503465</v>
       </c>
       <c r="AC64" t="n">
-        <v>4.22634228070089</v>
+        <v>61.97508794336452</v>
       </c>
       <c r="AD64" t="n">
-        <v>0.4610945537223199</v>
+        <v>0.3551300785993827</v>
       </c>
       <c r="AE64" t="n">
-        <v>3.696078893947096</v>
+        <v>61.75980855540762</v>
       </c>
       <c r="AF64" t="n">
-        <v>4.532991957815953</v>
+        <v>62.38498326022976</v>
       </c>
       <c r="AG64" t="n">
-        <v>0.3339287019737395</v>
+        <v>0.1957375911631123</v>
       </c>
       <c r="AH64" t="n">
-        <v>0.005922968216375502</v>
+        <v>0.00185789645218794</v>
       </c>
       <c r="AI64" t="n">
-        <v>0.3279016348982163</v>
+        <v>0.1943270421694492</v>
       </c>
       <c r="AJ64" t="n">
-        <v>0.3397417710698665</v>
+        <v>0.1978427023930701</v>
       </c>
       <c r="AK64" t="n">
-        <v>5.806724358161915</v>
+        <v>65.25015887548371</v>
       </c>
       <c r="AL64" t="n">
-        <v>0.5008577024775623</v>
+        <v>0.1366886164794673</v>
       </c>
       <c r="AM64" t="n">
-        <v>5.229336975799563</v>
+        <v>65.12229083491218</v>
       </c>
       <c r="AN64" t="n">
-        <v>6.124163416755338</v>
+        <v>65.39422466865246</v>
       </c>
       <c r="AO64" t="n">
-        <v>173.1171472582857</v>
+        <v>15.32567800203643</v>
       </c>
       <c r="AP64" t="n">
-        <v>15.70424906358834</v>
+        <v>0.0320931186662423</v>
       </c>
       <c r="AQ64" t="n">
-        <v>163.2876087636821</v>
+        <v>15.29187026938424</v>
       </c>
       <c r="AR64" t="n">
-        <v>191.2288316143751</v>
+        <v>15.35572516229571</v>
       </c>
       <c r="AS64" t="n">
-        <v>9.511033058166504</v>
+        <v>59.89662130673727</v>
       </c>
       <c r="AT64" t="n">
-        <v>0.8734549283126432</v>
+        <v>0.5549147881081347</v>
       </c>
       <c r="AU64" t="n">
-        <v>8.502555131912231</v>
+        <v>59.51439237594604</v>
       </c>
       <c r="AV64" t="n">
-        <v>10.02762985229492</v>
+        <v>60.53310775756836</v>
       </c>
       <c r="AW64" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX64" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY64" t="n">
-        <v>22.97621072776555</v>
+        <v>19.86799777064885</v>
       </c>
       <c r="AZ64" t="n">
-        <v>31.90496106468513</v>
+        <v>27.96394748528498</v>
       </c>
       <c r="BA64" t="n">
         <v>10.05440598105998</v>
@@ -30873,10 +30873,10 @@
         <v>99.58159847550684</v>
       </c>
       <c r="BC64" t="n">
-        <v>17.21803829926858</v>
+        <v>1.524274833431854</v>
       </c>
       <c r="BD64" t="n">
-        <v>94.16887813907692</v>
+        <v>34.47568639748971</v>
       </c>
       <c r="BE64" t="n">
         <v>3</v>
@@ -30923,136 +30923,136 @@
         </is>
       </c>
       <c r="I65" t="n">
-        <v>0.435271050241385</v>
+        <v>0.4264367120104848</v>
       </c>
       <c r="J65" t="n">
         <v>0</v>
       </c>
       <c r="K65" t="n">
-        <v>0.435271050241385</v>
+        <v>0.4264367120104848</v>
       </c>
       <c r="L65" t="n">
-        <v>0.435271050241385</v>
+        <v>0.4264367120104848</v>
       </c>
       <c r="M65" t="n">
-        <v>0.122124219307546</v>
+        <v>0.2174558723178378</v>
       </c>
       <c r="N65" t="n">
         <v>0</v>
       </c>
       <c r="O65" t="n">
-        <v>0.122124219307546</v>
+        <v>0.2174558723178378</v>
       </c>
       <c r="P65" t="n">
-        <v>0.122124219307546</v>
+        <v>0.2174558723178378</v>
       </c>
       <c r="Q65" t="n">
-        <v>0.1271027450111712</v>
+        <v>0.2184629615009358</v>
       </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>0.1271027450111712</v>
+        <v>0.2184629615009358</v>
       </c>
       <c r="T65" t="n">
-        <v>0.1271027450111712</v>
+        <v>0.2184629615009358</v>
       </c>
       <c r="U65" t="n">
-        <v>0.07292086991843209</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="V65" t="n">
         <v>0</v>
       </c>
       <c r="W65" t="n">
-        <v>0.07292086991843209</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="X65" t="n">
-        <v>0.07292086991843209</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="Y65" t="n">
-        <v>1.264734159831205</v>
+        <v>2.873127743759503</v>
       </c>
       <c r="Z65" t="n">
-        <v>0.04903726655368008</v>
+        <v>0.1748092207969942</v>
       </c>
       <c r="AA65" t="n">
-        <v>1.225113700016357</v>
+        <v>2.674301946975113</v>
       </c>
       <c r="AB65" t="n">
-        <v>1.319577486719936</v>
+        <v>3.002698403597825</v>
       </c>
       <c r="AC65" t="n">
-        <v>4.13728912889379</v>
+        <v>62.39494832289057</v>
       </c>
       <c r="AD65" t="n">
-        <v>0.2266987817737805</v>
+        <v>0.2073057914227061</v>
       </c>
       <c r="AE65" t="n">
-        <v>3.98111584937254</v>
+        <v>62.22300034939497</v>
       </c>
       <c r="AF65" t="n">
-        <v>4.397309184305304</v>
+        <v>62.62514821565203</v>
       </c>
       <c r="AG65" t="n">
-        <v>0.3287510277216762</v>
+        <v>0.1969462421705002</v>
       </c>
       <c r="AH65" t="n">
-        <v>0.005223496850763121</v>
+        <v>0.00114446247561792</v>
       </c>
       <c r="AI65" t="n">
-        <v>0.3234090602427934</v>
+        <v>0.1961259855525862</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0.3338473891514684</v>
+        <v>0.1982536879643385</v>
       </c>
       <c r="AK65" t="n">
-        <v>5.730774316446671</v>
+        <v>65.46502230882056</v>
       </c>
       <c r="AL65" t="n">
-        <v>0.2801329701343132</v>
+        <v>0.3415133986578889</v>
       </c>
       <c r="AM65" t="n">
-        <v>5.52963860963169</v>
+        <v>65.09376134936466</v>
       </c>
       <c r="AN65" t="n">
-        <v>6.050734060176709</v>
+        <v>65.76578478432194</v>
       </c>
       <c r="AO65" t="n">
-        <v>174.7680069492684</v>
+        <v>15.27561033568467</v>
       </c>
       <c r="AP65" t="n">
-        <v>8.332427585108709</v>
+        <v>0.07981297522027106</v>
       </c>
       <c r="AQ65" t="n">
-        <v>165.269203712251</v>
+        <v>15.20547505484026</v>
       </c>
       <c r="AR65" t="n">
-        <v>180.8436446928322</v>
+        <v>15.36245531477128</v>
       </c>
       <c r="AS65" t="n">
-        <v>9.38656465212504</v>
+        <v>59.87548462549845</v>
       </c>
       <c r="AT65" t="n">
-        <v>0.5046643599620714</v>
+        <v>0.2164089369077034</v>
       </c>
       <c r="AU65" t="n">
-        <v>9.04016900062561</v>
+        <v>59.67401480674744</v>
       </c>
       <c r="AV65" t="n">
-        <v>9.96558713912964</v>
+        <v>60.10424399375916</v>
       </c>
       <c r="AW65" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX65" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY65" t="n">
-        <v>86.41267307288531</v>
+        <v>76.69773960516709</v>
       </c>
       <c r="AZ65" t="n">
-        <v>90.93202006388174</v>
+        <v>84.29634297168512</v>
       </c>
       <c r="BA65" t="n">
         <v>9.903624659284763</v>
@@ -31061,10 +31061,10 @@
         <v>100.9767087666561</v>
       </c>
       <c r="BC65" t="n">
-        <v>17.64687303505806</v>
+        <v>1.542426218805012</v>
       </c>
       <c r="BD65" t="n">
-        <v>94.32465725369428</v>
+        <v>35.16819560825494</v>
       </c>
       <c r="BE65" t="n">
         <v>3</v>
@@ -31977,130 +31977,130 @@
         </is>
       </c>
       <c r="I5" t="n">
-        <v>0.8963520100241514</v>
+        <v>0.8861158550177132</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>0.8963520100241514</v>
+        <v>0.8861158550177131</v>
       </c>
       <c r="L5" t="n">
-        <v>0.8963520100241514</v>
+        <v>0.8861158550177131</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8660765626746049</v>
+        <v>0.8829669114684049</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8660765626746049</v>
+        <v>0.8829669114684049</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8660765626746049</v>
+        <v>0.8829669114684049</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="T5" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="X5" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.195114706416027</v>
+        <v>3.459603306828011</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.07245072200281331</v>
+        <v>0.1029811123327931</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.11392816382589</v>
+        <v>3.389318269883992</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.253191286763555</v>
+        <v>3.577812784336889</v>
       </c>
       <c r="AC5" t="n">
-        <v>3.739857279515308</v>
+        <v>62.7695173104398</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.4305006474917559</v>
+        <v>0.8454500031771928</v>
       </c>
       <c r="AE5" t="n">
-        <v>3.331245740935037</v>
+        <v>62.19613654096213</v>
       </c>
       <c r="AF5" t="n">
-        <v>4.189332919293476</v>
+        <v>63.74046757107902</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.3214192212893919</v>
+        <v>0.1961919489942199</v>
       </c>
       <c r="AH5" t="n">
-        <v>0.02057036352137559</v>
+        <v>0.002596063948170386</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.2981121217024075</v>
+        <v>0.1931943999960526</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.3370381445877804</v>
+        <v>0.1977146614480952</v>
       </c>
       <c r="AK5" t="n">
-        <v>5.256391207220727</v>
+        <v>66.42531256626202</v>
       </c>
       <c r="AL5" t="n">
-        <v>0.5182114893728951</v>
+        <v>0.8007284624570832</v>
       </c>
       <c r="AM5" t="n">
-        <v>4.743286026463334</v>
+        <v>65.95446048915828</v>
       </c>
       <c r="AN5" t="n">
-        <v>5.779562350644812</v>
+        <v>67.34986109879026</v>
       </c>
       <c r="AO5" t="n">
-        <v>191.4857997151397</v>
+        <v>15.05595045746269</v>
       </c>
       <c r="AP5" t="n">
-        <v>18.91563971862029</v>
+        <v>0.1802392310244332</v>
       </c>
       <c r="AQ5" t="n">
-        <v>173.023481594317</v>
+        <v>14.84784056990374</v>
       </c>
       <c r="AR5" t="n">
-        <v>210.824309228009</v>
+        <v>15.16197680313649</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.783390124638876</v>
+        <v>60.83974011739095</v>
       </c>
       <c r="AT5" t="n">
-        <v>0.8521905829646145</v>
+        <v>0.9823820398093274</v>
       </c>
       <c r="AU5" t="n">
-        <v>7.919425487518311</v>
+        <v>60.18165683746338</v>
       </c>
       <c r="AV5" t="n">
-        <v>9.623297214508057</v>
+        <v>61.96895003318787</v>
       </c>
       <c r="AW5" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX5" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
@@ -32115,10 +32115,10 @@
         <v>97.3445537305448</v>
       </c>
       <c r="BC5" t="n">
-        <v>18.63826646505563</v>
+        <v>1.465470635046152</v>
       </c>
       <c r="BD5" t="n">
-        <v>94.60022055083768</v>
+        <v>31.76268212176408</v>
       </c>
       <c r="BE5" t="n">
         <v>3</v>
@@ -35271,136 +35271,136 @@
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0.6807838867983227</v>
+        <v>0.6299930781790891</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6807838867983227</v>
+        <v>0.6299930781790891</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6807838867983227</v>
+        <v>0.6299930781790891</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4938162375024422</v>
+        <v>0.5236990023280943</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4938162375024422</v>
+        <v>0.5236990023280943</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4938162375024422</v>
+        <v>0.5236990023280943</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.5214984470712496</v>
+        <v>0.5807748643741676</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.5214984470712496</v>
+        <v>0.5807748643741676</v>
       </c>
       <c r="T17" t="n">
-        <v>0.5214984470712496</v>
+        <v>0.5807748643741676</v>
       </c>
       <c r="U17" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="X17" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="Y17" t="n">
-        <v>1.240890381119375</v>
+        <v>3.07401487108204</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.02291066127572707</v>
+        <v>0.03963301017321692</v>
       </c>
       <c r="AA17" t="n">
-        <v>1.215600822889614</v>
+        <v>3.035289937345197</v>
       </c>
       <c r="AB17" t="n">
-        <v>1.260260268671951</v>
+        <v>3.114497473501593</v>
       </c>
       <c r="AC17" t="n">
-        <v>4.036811780340313</v>
+        <v>61.68362194618701</v>
       </c>
       <c r="AD17" t="n">
-        <v>0.1936570828221393</v>
+        <v>2.622065695103189</v>
       </c>
       <c r="AE17" t="n">
-        <v>3.836754749436405</v>
+        <v>60.14954761686918</v>
       </c>
       <c r="AF17" t="n">
-        <v>4.223361703643824</v>
+        <v>64.71123215180988</v>
       </c>
       <c r="AG17" t="n">
-        <v>0.343587698396542</v>
+        <v>0.1885085064330554</v>
       </c>
       <c r="AH17" t="n">
-        <v>0.02059602669422079</v>
+        <v>0.001975656568859066</v>
       </c>
       <c r="AI17" t="n">
-        <v>0.3256693349744253</v>
+        <v>0.1863357096445692</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0.3660892397540492</v>
+        <v>0.1901969301299511</v>
       </c>
       <c r="AK17" t="n">
-        <v>5.621289859856229</v>
+        <v>64.94614532370211</v>
       </c>
       <c r="AL17" t="n">
-        <v>0.2304245714581085</v>
+        <v>2.65850857002784</v>
       </c>
       <c r="AM17" t="n">
-        <v>5.378024907300444</v>
+        <v>63.41079769879315</v>
       </c>
       <c r="AN17" t="n">
-        <v>5.836260995194432</v>
+        <v>68.01592655544142</v>
       </c>
       <c r="AO17" t="n">
-        <v>178.0962129130423</v>
+        <v>15.41419372853648</v>
       </c>
       <c r="AP17" t="n">
-        <v>7.360652628863323</v>
+        <v>0.6163978293862388</v>
       </c>
       <c r="AQ17" t="n">
-        <v>171.3425771779909</v>
+        <v>14.70243883518775</v>
       </c>
       <c r="AR17" t="n">
-        <v>185.941868480851</v>
+        <v>15.77018483114008</v>
       </c>
       <c r="AS17" t="n">
-        <v>9.47118059794108</v>
+        <v>60.12889409065247</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.3487614145643093</v>
+        <v>2.789103668801163</v>
       </c>
       <c r="AU17" t="n">
-        <v>9.07709002494812</v>
+        <v>58.4327507019043</v>
       </c>
       <c r="AV17" t="n">
-        <v>9.740017175674438</v>
+        <v>63.34791970252991</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX17" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY17" t="n">
-        <v>44.25163758881126</v>
+        <v>38.0518920578551</v>
       </c>
       <c r="AZ17" t="n">
-        <v>53.69159129775718</v>
+        <v>49.80363132446787</v>
       </c>
       <c r="BA17" t="n">
         <v>10.46560356014806</v>
@@ -35409,10 +35409,10 @@
         <v>95.55230161727472</v>
       </c>
       <c r="BC17" t="n">
-        <v>17.01729020113224</v>
+        <v>1.472843266033136</v>
       </c>
       <c r="BD17" t="n">
-        <v>94.11705446680735</v>
+        <v>32.03078918618051</v>
       </c>
       <c r="BE17" t="n">
         <v>3</v>
@@ -35459,136 +35459,136 @@
         </is>
       </c>
       <c r="I18" t="n">
-        <v>0.9045575585741988</v>
+        <v>0.8297052480181289</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.9045575585741988</v>
+        <v>0.8297052480181289</v>
       </c>
       <c r="L18" t="n">
-        <v>0.9045575585741988</v>
+        <v>0.8297052480181289</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7456976377342096</v>
+        <v>0.8295355941953315</v>
       </c>
       <c r="N18" t="n">
         <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7456976377342096</v>
+        <v>0.8295355941953315</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7456976377342096</v>
+        <v>0.8295355941953315</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.8870791824205587</v>
+        <v>0.8832205855459415</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>0.8870791824205587</v>
+        <v>0.8832205855459414</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8870791824205587</v>
+        <v>0.8832205855459414</v>
       </c>
       <c r="U18" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="X18" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="Y18" t="n">
-        <v>1.256413232551429</v>
+        <v>2.170604326501742</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.08557543818342471</v>
+        <v>0.747060109868215</v>
       </c>
       <c r="AA18" t="n">
-        <v>1.159636200062811</v>
+        <v>1.717446163850702</v>
       </c>
       <c r="AB18" t="n">
-        <v>1.322087873500479</v>
+        <v>3.03285987229119</v>
       </c>
       <c r="AC18" t="n">
-        <v>4.036828275496531</v>
+        <v>60.91332641565706</v>
       </c>
       <c r="AD18" t="n">
-        <v>0.477536103150557</v>
+        <v>0.984809524561593</v>
       </c>
       <c r="AE18" t="n">
-        <v>3.487645795207919</v>
+        <v>60.31156338191199</v>
       </c>
       <c r="AF18" t="n">
-        <v>4.354311033686432</v>
+        <v>62.04982790481406</v>
       </c>
       <c r="AG18" t="n">
-        <v>0.3306661775178988</v>
+        <v>0.1782652168703022</v>
       </c>
       <c r="AH18" t="n">
-        <v>0.02295517200809089</v>
+        <v>0.009965861787121668</v>
       </c>
       <c r="AI18" t="n">
-        <v>0.3064756710736252</v>
+        <v>0.1693475192803225</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.3521451650925313</v>
+        <v>0.1890228277206696</v>
       </c>
       <c r="AK18" t="n">
-        <v>5.623907685565858</v>
+        <v>63.26219595902911</v>
       </c>
       <c r="AL18" t="n">
-        <v>0.5845208049174803</v>
+        <v>0.9414420756640458</v>
       </c>
       <c r="AM18" t="n">
-        <v>4.953757666344354</v>
+        <v>62.19835706504301</v>
       </c>
       <c r="AN18" t="n">
-        <v>6.028544072279443</v>
+        <v>63.98776015178731</v>
       </c>
       <c r="AO18" t="n">
-        <v>179.1801529681308</v>
+        <v>15.80957932906928</v>
       </c>
       <c r="AP18" t="n">
-        <v>19.74479542964937</v>
+        <v>0.2369355231746624</v>
       </c>
       <c r="AQ18" t="n">
-        <v>165.8775299658532</v>
+        <v>15.62798881579648</v>
       </c>
       <c r="AR18" t="n">
-        <v>201.8669598624016</v>
+        <v>16.07759508750793</v>
       </c>
       <c r="AS18" t="n">
-        <v>9.444903294245401</v>
+        <v>58.29159593582153</v>
       </c>
       <c r="AT18" t="n">
-        <v>0.9514204125006295</v>
+        <v>1.300752034568336</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.348035335540771</v>
+        <v>56.87005281448364</v>
       </c>
       <c r="AV18" t="n">
-        <v>10.04682850837708</v>
+        <v>59.42232847213745</v>
       </c>
       <c r="AW18" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX18" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY18" t="n">
-        <v>5.170931904528223</v>
+        <v>5.791645736798458</v>
       </c>
       <c r="AZ18" t="n">
-        <v>9.866175606361049</v>
+        <v>8.951380806422364</v>
       </c>
       <c r="BA18" t="n">
         <v>10.42768617105556</v>
@@ -35597,10 +35597,10 @@
         <v>95.90044595903659</v>
       </c>
       <c r="BC18" t="n">
-        <v>17.18311713920645</v>
+        <v>1.51611575854214</v>
       </c>
       <c r="BD18" t="n">
-        <v>94.13568140447639</v>
+        <v>34.03347051581883</v>
       </c>
       <c r="BE18" t="n">
         <v>3</v>
@@ -35647,136 +35647,136 @@
         </is>
       </c>
       <c r="I19" t="n">
-        <v>0.8888511745802176</v>
+        <v>0.9007242709230804</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.8888511745802176</v>
+        <v>0.9007242709230804</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8888511745802176</v>
+        <v>0.9007242709230804</v>
       </c>
       <c r="M19" t="n">
-        <v>0.8423088650259937</v>
+        <v>0.8634411034374985</v>
       </c>
       <c r="N19" t="n">
         <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8423088650259938</v>
+        <v>0.8634411034374985</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8423088650259938</v>
+        <v>0.8634411034374985</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.920816621002182</v>
+        <v>0.9232057676193612</v>
       </c>
       <c r="R19" t="n">
         <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.920816621002182</v>
+        <v>0.9232057676193612</v>
       </c>
       <c r="T19" t="n">
-        <v>0.920816621002182</v>
+        <v>0.9232057676193612</v>
       </c>
       <c r="U19" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="X19" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="Y19" t="n">
-        <v>1.215081399569758</v>
+        <v>2.823390071484189</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.04509922180845374</v>
+        <v>0.5369609153102619</v>
       </c>
       <c r="AA19" t="n">
-        <v>1.168852561401643</v>
+        <v>2.20589367469918</v>
       </c>
       <c r="AB19" t="n">
-        <v>1.258959024065018</v>
+        <v>3.180622025290056</v>
       </c>
       <c r="AC19" t="n">
-        <v>3.864816064655695</v>
+        <v>61.4326239843324</v>
       </c>
       <c r="AD19" t="n">
-        <v>0.4834258030646357</v>
+        <v>0.3006996045912227</v>
       </c>
       <c r="AE19" t="n">
-        <v>3.465931490374868</v>
+        <v>61.13945347229586</v>
       </c>
       <c r="AF19" t="n">
-        <v>4.402442960211824</v>
+        <v>61.74032578312481</v>
       </c>
       <c r="AG19" t="n">
-        <v>0.3269186136759274</v>
+        <v>0.1977847899641814</v>
       </c>
       <c r="AH19" t="n">
-        <v>0.02090250728227047</v>
+        <v>0.001400571269237281</v>
       </c>
       <c r="AI19" t="n">
-        <v>0.3117338686999836</v>
+        <v>0.1966948734941278</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.3507585229217292</v>
+        <v>0.199364475915297</v>
       </c>
       <c r="AK19" t="n">
-        <v>5.40681607790138</v>
+        <v>64.45379884578078</v>
       </c>
       <c r="AL19" t="n">
-        <v>0.5474279371725285</v>
+        <v>0.6504588154688254</v>
       </c>
       <c r="AM19" t="n">
-        <v>4.946517920476494</v>
+        <v>63.82068124576985</v>
       </c>
       <c r="AN19" t="n">
-        <v>6.01216050719857</v>
+        <v>65.12031228433017</v>
       </c>
       <c r="AO19" t="n">
-        <v>186.1806981698334</v>
+        <v>15.51604202231935</v>
       </c>
       <c r="AP19" t="n">
-        <v>18.22711485469044</v>
+        <v>0.1564722947781896</v>
       </c>
       <c r="AQ19" t="n">
-        <v>166.3295580353627</v>
+        <v>15.35619171532488</v>
       </c>
       <c r="AR19" t="n">
-        <v>202.1624132524462</v>
+        <v>15.66890199979308</v>
       </c>
       <c r="AS19" t="n">
-        <v>8.934955755869547</v>
+        <v>59.32744558652242</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.8222815666111919</v>
+        <v>0.8598111715155307</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.191219329833984</v>
+        <v>58.35378503799439</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.817988395690918</v>
+        <v>59.98239517211914</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX19" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY19" t="n">
-        <v>1.564388177626981</v>
+        <v>1.526643018680312</v>
       </c>
       <c r="AZ19" t="n">
-        <v>4.614860405212791</v>
+        <v>4.183858364223433</v>
       </c>
       <c r="BA19" t="n">
         <v>10.23204564484659</v>
@@ -35785,10 +35785,10 @@
         <v>97.74566249718235</v>
       </c>
       <c r="BC19" t="n">
-        <v>18.19584320009401</v>
+        <v>1.516416419636876</v>
       </c>
       <c r="BD19" t="n">
-        <v>94.46848490278815</v>
+        <v>34.05968387841379</v>
       </c>
       <c r="BE19" t="n">
         <v>3</v>
@@ -35835,136 +35835,136 @@
         </is>
       </c>
       <c r="I20" t="n">
-        <v>0.8366387179945584</v>
+        <v>0.8662210580690296</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8366387179945585</v>
+        <v>0.8662210580690296</v>
       </c>
       <c r="L20" t="n">
-        <v>0.8366387179945585</v>
+        <v>0.8662210580690296</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8299938487051532</v>
+        <v>0.8412129116577401</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8299938487051532</v>
+        <v>0.8412129116577401</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8299938487051532</v>
+        <v>0.8412129116577401</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.9002848662126398</v>
+        <v>0.9235417287411419</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9002848662126398</v>
+        <v>0.923541728741142</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9002848662126398</v>
+        <v>0.923541728741142</v>
       </c>
       <c r="U20" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416777</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416778</v>
       </c>
       <c r="X20" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416778</v>
       </c>
       <c r="Y20" t="n">
-        <v>1.273206406041578</v>
+        <v>3.084528051404671</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.04377367211860447</v>
+        <v>0.1277287731654614</v>
       </c>
       <c r="AA20" t="n">
-        <v>1.242350834976364</v>
+        <v>2.955306515659357</v>
       </c>
       <c r="AB20" t="n">
-        <v>1.323305284309009</v>
+        <v>3.210709798797478</v>
       </c>
       <c r="AC20" t="n">
-        <v>4.226664143777406</v>
+        <v>62.07660985541878</v>
       </c>
       <c r="AD20" t="n">
-        <v>0.3308915886694174</v>
+        <v>0.2054515466693488</v>
       </c>
       <c r="AE20" t="n">
-        <v>3.878452881949067</v>
+        <v>61.95215227952736</v>
       </c>
       <c r="AF20" t="n">
-        <v>4.536971578292365</v>
+        <v>62.31374739637946</v>
       </c>
       <c r="AG20" t="n">
-        <v>0.3236632711008839</v>
+        <v>0.1970441405613468</v>
       </c>
       <c r="AH20" t="n">
-        <v>0.005544551874649899</v>
+        <v>0.0004664107564050874</v>
       </c>
       <c r="AI20" t="n">
-        <v>0.319656326537808</v>
+        <v>0.1966932481892915</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0.329991133737375</v>
+        <v>0.1975734156624102</v>
       </c>
       <c r="AK20" t="n">
-        <v>5.823533820919867</v>
+        <v>65.3581820473848</v>
       </c>
       <c r="AL20" t="n">
-        <v>0.3751709323693725</v>
+        <v>0.2414832094330966</v>
       </c>
       <c r="AM20" t="n">
-        <v>5.44046004346324</v>
+        <v>65.11592965419817</v>
       </c>
       <c r="AN20" t="n">
-        <v>6.190267996338749</v>
+        <v>65.59888865179904</v>
       </c>
       <c r="AO20" t="n">
-        <v>172.1961559852246</v>
+        <v>15.30044242337567</v>
       </c>
       <c r="AP20" t="n">
-        <v>11.16301990987924</v>
+        <v>0.05653395056725858</v>
       </c>
       <c r="AQ20" t="n">
-        <v>161.5438944794398</v>
+        <v>15.24416069467322</v>
       </c>
       <c r="AR20" t="n">
-        <v>183.8079853562216</v>
+        <v>15.3572252643947</v>
       </c>
       <c r="AS20" t="n">
-        <v>9.59859307607015</v>
+        <v>60.66661739349365</v>
       </c>
       <c r="AT20" t="n">
-        <v>0.5041514544200026</v>
+        <v>0.1368778697374766</v>
       </c>
       <c r="AU20" t="n">
-        <v>9.060518503189089</v>
+        <v>60.51085138320923</v>
       </c>
       <c r="AV20" t="n">
-        <v>10.06005048751831</v>
+        <v>60.76770091056824</v>
       </c>
       <c r="AW20" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX20" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY20" t="n">
-        <v>3.759239789119267</v>
+        <v>1.490807866174425</v>
       </c>
       <c r="AZ20" t="n">
-        <v>4.93796172305524</v>
+        <v>2.002068621107012</v>
       </c>
       <c r="BA20" t="n">
         <v>10.58551849793414</v>
@@ -35973,10 +35973,10 @@
         <v>94.4711289337143</v>
       </c>
       <c r="BC20" t="n">
-        <v>16.26714421394004</v>
+        <v>1.445412657524682</v>
       </c>
       <c r="BD20" t="n">
-        <v>93.83564705254454</v>
+        <v>30.81676615377022</v>
       </c>
       <c r="BE20" t="n">
         <v>3</v>
@@ -36023,136 +36023,136 @@
         </is>
       </c>
       <c r="I21" t="n">
-        <v>0.435271050241385</v>
+        <v>0.4264367120104848</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>0.435271050241385</v>
+        <v>0.4264367120104848</v>
       </c>
       <c r="L21" t="n">
-        <v>0.435271050241385</v>
+        <v>0.4264367120104848</v>
       </c>
       <c r="M21" t="n">
-        <v>0.122124219307546</v>
+        <v>0.2174558723178378</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.122124219307546</v>
+        <v>0.2174558723178378</v>
       </c>
       <c r="P21" t="n">
-        <v>0.122124219307546</v>
+        <v>0.2174558723178378</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.1271027450111712</v>
+        <v>0.2184629615009358</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>0.1271027450111712</v>
+        <v>0.2184629615009358</v>
       </c>
       <c r="T21" t="n">
-        <v>0.1271027450111712</v>
+        <v>0.2184629615009358</v>
       </c>
       <c r="U21" t="n">
-        <v>0.07292086991843209</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.07292086991843209</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="X21" t="n">
-        <v>0.07292086991843209</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="Y21" t="n">
-        <v>1.264734159831205</v>
+        <v>2.873127743759503</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.04903726655368008</v>
+        <v>0.1748092207969942</v>
       </c>
       <c r="AA21" t="n">
-        <v>1.225113700016357</v>
+        <v>2.674301946975113</v>
       </c>
       <c r="AB21" t="n">
-        <v>1.319577486719936</v>
+        <v>3.002698403597825</v>
       </c>
       <c r="AC21" t="n">
-        <v>4.13728912889379</v>
+        <v>62.39494832289057</v>
       </c>
       <c r="AD21" t="n">
-        <v>0.2266987817737805</v>
+        <v>0.2073057914227061</v>
       </c>
       <c r="AE21" t="n">
-        <v>3.98111584937254</v>
+        <v>62.22300034939497</v>
       </c>
       <c r="AF21" t="n">
-        <v>4.397309184305304</v>
+        <v>62.62514821565203</v>
       </c>
       <c r="AG21" t="n">
-        <v>0.3287510277216762</v>
+        <v>0.1969462421705002</v>
       </c>
       <c r="AH21" t="n">
-        <v>0.005223496850763121</v>
+        <v>0.00114446247561792</v>
       </c>
       <c r="AI21" t="n">
-        <v>0.3234090602427934</v>
+        <v>0.1961259855525862</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0.3338473891514684</v>
+        <v>0.1982536879643385</v>
       </c>
       <c r="AK21" t="n">
-        <v>5.730774316446671</v>
+        <v>65.46502230882056</v>
       </c>
       <c r="AL21" t="n">
-        <v>0.2801329701343132</v>
+        <v>0.3415133986578889</v>
       </c>
       <c r="AM21" t="n">
-        <v>5.52963860963169</v>
+        <v>65.09376134936466</v>
       </c>
       <c r="AN21" t="n">
-        <v>6.050734060176709</v>
+        <v>65.76578478432194</v>
       </c>
       <c r="AO21" t="n">
-        <v>174.7680069492684</v>
+        <v>15.27561033568467</v>
       </c>
       <c r="AP21" t="n">
-        <v>8.332427585108709</v>
+        <v>0.07981297522027106</v>
       </c>
       <c r="AQ21" t="n">
-        <v>165.269203712251</v>
+        <v>15.20547505484026</v>
       </c>
       <c r="AR21" t="n">
-        <v>180.8436446928322</v>
+        <v>15.36245531477128</v>
       </c>
       <c r="AS21" t="n">
-        <v>9.38656465212504</v>
+        <v>59.87548462549845</v>
       </c>
       <c r="AT21" t="n">
-        <v>0.5046643599620714</v>
+        <v>0.2164089369077034</v>
       </c>
       <c r="AU21" t="n">
-        <v>9.04016900062561</v>
+        <v>59.67401480674744</v>
       </c>
       <c r="AV21" t="n">
-        <v>9.96558713912964</v>
+        <v>60.10424399375916</v>
       </c>
       <c r="AW21" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="AX21" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="AY21" t="n">
-        <v>86.41267307288531</v>
+        <v>76.69773960516709</v>
       </c>
       <c r="AZ21" t="n">
-        <v>90.93202006388174</v>
+        <v>84.29634297168512</v>
       </c>
       <c r="BA21" t="n">
         <v>9.903624659284763</v>
@@ -36161,10 +36161,10 @@
         <v>100.9767087666561</v>
       </c>
       <c r="BC21" t="n">
-        <v>17.64687303505806</v>
+        <v>1.542426218805012</v>
       </c>
       <c r="BD21" t="n">
-        <v>94.32465725369428</v>
+        <v>35.16819560825494</v>
       </c>
       <c r="BE21" t="n">
         <v>3</v>
@@ -38330,10 +38330,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>0.9354507011789542</v>
+        <v>0.9375183256873152</v>
       </c>
       <c r="F50" t="n">
-        <v>0.8041578216112298</v>
+        <v>0.8106194405984933</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -38342,13 +38342,13 @@
         <v>0</v>
       </c>
       <c r="I50" t="n">
-        <v>191.4857997151397</v>
+        <v>15.05595045746269</v>
       </c>
       <c r="J50" t="n">
-        <v>5.256391207220727</v>
+        <v>66.42531256626202</v>
       </c>
       <c r="K50" t="n">
-        <v>18.63826646505563</v>
+        <v>1.465470635046152</v>
       </c>
     </row>
     <row r="51">
@@ -38373,25 +38373,25 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>0.8972129987083401</v>
+        <v>0.9138390369805568</v>
       </c>
       <c r="F51" t="n">
-        <v>0.7578056823174325</v>
+        <v>0.779266846434712</v>
       </c>
       <c r="G51" t="n">
-        <v>4.08762347630109</v>
+        <v>2.525741423710154</v>
       </c>
       <c r="H51" t="n">
-        <v>5.764059995204061</v>
+        <v>3.867732821782958</v>
       </c>
       <c r="I51" t="n">
-        <v>189.0894238198177</v>
+        <v>15.16108460988195</v>
       </c>
       <c r="J51" t="n">
-        <v>5.318910469451152</v>
+        <v>65.9694899269016</v>
       </c>
       <c r="K51" t="n">
-        <v>17.94560891134081</v>
+        <v>1.4388689202414</v>
       </c>
     </row>
     <row r="52">
@@ -38416,25 +38416,25 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>0.7707737698172715</v>
+        <v>0.7787717652837904</v>
       </c>
       <c r="F52" t="n">
-        <v>0.6240064954710411</v>
+        <v>0.6254110464216518</v>
       </c>
       <c r="G52" t="n">
-        <v>17.6040203031693</v>
+        <v>16.9326354540477</v>
       </c>
       <c r="H52" t="n">
-        <v>22.40248385313634</v>
+        <v>22.84776121827268</v>
       </c>
       <c r="I52" t="n">
-        <v>183.1573852046965</v>
+        <v>14.72425285512592</v>
       </c>
       <c r="J52" t="n">
-        <v>5.497979681962146</v>
+        <v>67.93632836024499</v>
       </c>
       <c r="K52" t="n">
-        <v>17.56522383025416</v>
+        <v>1.412090464408496</v>
       </c>
     </row>
     <row r="53">
@@ -38459,25 +38459,25 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>0.5214984470712496</v>
+        <v>0.5807748643741676</v>
       </c>
       <c r="F53" t="n">
-        <v>0.372392690642781</v>
+        <v>0.406901522958356</v>
       </c>
       <c r="G53" t="n">
-        <v>44.25163758881126</v>
+        <v>38.0518920578551</v>
       </c>
       <c r="H53" t="n">
-        <v>53.69159129775718</v>
+        <v>49.80363132446787</v>
       </c>
       <c r="I53" t="n">
-        <v>178.0962129130423</v>
+        <v>15.41419372853648</v>
       </c>
       <c r="J53" t="n">
-        <v>5.621289859856229</v>
+        <v>64.94614532370211</v>
       </c>
       <c r="K53" t="n">
-        <v>17.01729020113224</v>
+        <v>1.472843266033136</v>
       </c>
     </row>
     <row r="54">
@@ -38502,25 +38502,25 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>0.9183375572963554</v>
+        <v>0.9190307552534428</v>
       </c>
       <c r="F54" t="n">
-        <v>0.7868302589310699</v>
+        <v>0.7960427176781358</v>
       </c>
       <c r="G54" t="n">
-        <v>1.829400935937199</v>
+        <v>1.97196896608061</v>
       </c>
       <c r="H54" t="n">
-        <v>2.154746520458132</v>
+        <v>1.798220248652718</v>
       </c>
       <c r="I54" t="n">
-        <v>175.9091726081195</v>
+        <v>15.96760692109466</v>
       </c>
       <c r="J54" t="n">
-        <v>5.701664354279661</v>
+        <v>62.62716871285766</v>
       </c>
       <c r="K54" t="n">
-        <v>17.41679229124517</v>
+        <v>1.580955040658965</v>
       </c>
     </row>
     <row r="55">
@@ -38545,25 +38545,25 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>0.8903329101751702</v>
+        <v>0.9007055798541789</v>
       </c>
       <c r="F55" t="n">
-        <v>0.7480057530889145</v>
+        <v>0.7730690891765476</v>
       </c>
       <c r="G55" t="n">
-        <v>4.823107294368561</v>
+        <v>3.926616133732436</v>
       </c>
       <c r="H55" t="n">
-        <v>6.982717448399336</v>
+        <v>4.632303340050877</v>
       </c>
       <c r="I55" t="n">
-        <v>178.4642013566757</v>
+        <v>15.65491672489611</v>
       </c>
       <c r="J55" t="n">
-        <v>5.662681179918979</v>
+        <v>63.90097056987999</v>
       </c>
       <c r="K55" t="n">
-        <v>17.51450102386532</v>
+        <v>1.53637565922104</v>
       </c>
     </row>
     <row r="56">
@@ -38588,25 +38588,25 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>0.8870791824205587</v>
+        <v>0.8832205855459415</v>
       </c>
       <c r="F56" t="n">
-        <v>0.7248181987787783</v>
+        <v>0.7380578075796315</v>
       </c>
       <c r="G56" t="n">
-        <v>5.170931904528223</v>
+        <v>5.791645736798458</v>
       </c>
       <c r="H56" t="n">
-        <v>9.866175606361049</v>
+        <v>8.951380806422364</v>
       </c>
       <c r="I56" t="n">
-        <v>179.1801529681308</v>
+        <v>15.80957932906928</v>
       </c>
       <c r="J56" t="n">
-        <v>5.623907685565858</v>
+        <v>63.26219595902911</v>
       </c>
       <c r="K56" t="n">
-        <v>17.18311713920645</v>
+        <v>1.51611575854214</v>
       </c>
     </row>
     <row r="57">
@@ -38631,25 +38631,25 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>0.9344103520410755</v>
+        <v>0.9362675415983444</v>
       </c>
       <c r="F57" t="n">
-        <v>0.7952145538510432</v>
+        <v>0.808555114657571</v>
       </c>
       <c r="G57" t="n">
-        <v>0.1112136787719119</v>
+        <v>0.1334143615863571</v>
       </c>
       <c r="H57" t="n">
-        <v>1.112128430494858</v>
+        <v>0.2546603051363033</v>
       </c>
       <c r="I57" t="n">
-        <v>179.1555669158573</v>
+        <v>15.43430277843191</v>
       </c>
       <c r="J57" t="n">
-        <v>5.597804468285527</v>
+        <v>64.79568787349434</v>
       </c>
       <c r="K57" t="n">
-        <v>17.93503056565607</v>
+        <v>1.54510795760411</v>
       </c>
     </row>
     <row r="58">
@@ -38674,25 +38674,25 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>0.9083748763111515</v>
+        <v>0.9345543815455292</v>
       </c>
       <c r="F58" t="n">
-        <v>0.7699517482344933</v>
+        <v>0.8062458515669091</v>
       </c>
       <c r="G58" t="n">
-        <v>2.89441494176859</v>
+        <v>0.3161478619218554</v>
       </c>
       <c r="H58" t="n">
-        <v>4.253651765545279</v>
+        <v>0.5395366570970905</v>
       </c>
       <c r="I58" t="n">
-        <v>177.33409022152</v>
+        <v>15.51282872118186</v>
       </c>
       <c r="J58" t="n">
-        <v>5.696113400008618</v>
+        <v>64.46315985341083</v>
       </c>
       <c r="K58" t="n">
-        <v>17.53957063945782</v>
+        <v>1.534326281162835</v>
       </c>
     </row>
     <row r="59">
@@ -38717,25 +38717,25 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>0.920816621002182</v>
+        <v>0.9232057676193612</v>
       </c>
       <c r="F59" t="n">
-        <v>0.7670470607062715</v>
+        <v>0.7767042713309921</v>
       </c>
       <c r="G59" t="n">
-        <v>1.564388177626981</v>
+        <v>1.526643018680312</v>
       </c>
       <c r="H59" t="n">
-        <v>4.614860405212791</v>
+        <v>4.183858364223433</v>
       </c>
       <c r="I59" t="n">
-        <v>186.1806981698334</v>
+        <v>15.51604202231935</v>
       </c>
       <c r="J59" t="n">
-        <v>5.40681607790138</v>
+        <v>64.45379884578078</v>
       </c>
       <c r="K59" t="n">
-        <v>18.19584320009401</v>
+        <v>1.516416419636876</v>
       </c>
     </row>
     <row r="60">
@@ -38760,25 +38760,25 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>0.9344102707423176</v>
+        <v>0.9324929045585608</v>
       </c>
       <c r="F60" t="n">
-        <v>0.7969907346365336</v>
+        <v>0.8003892058753374</v>
       </c>
       <c r="G60" t="n">
-        <v>0.1112223696369393</v>
+        <v>0.536034442320914</v>
       </c>
       <c r="H60" t="n">
-        <v>0.8912537790574629</v>
+        <v>1.262026816875109</v>
       </c>
       <c r="I60" t="n">
-        <v>179.5480752440816</v>
+        <v>15.56937934229981</v>
       </c>
       <c r="J60" t="n">
-        <v>5.593409956630178</v>
+        <v>64.23080079878356</v>
       </c>
       <c r="K60" t="n">
-        <v>17.09403711953927</v>
+        <v>1.482296861404164</v>
       </c>
     </row>
     <row r="61">
@@ -38803,25 +38803,25 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>0.933442221253304</v>
+        <v>0.9286825537818112</v>
       </c>
       <c r="F61" t="n">
-        <v>0.8022050375687061</v>
+        <v>0.8024096003660924</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2147071912094278</v>
+        <v>0.942463913868169</v>
       </c>
       <c r="H61" t="n">
-        <v>0.2428359197714576</v>
+        <v>1.012786003052116</v>
       </c>
       <c r="I61" t="n">
-        <v>174.7178585323763</v>
+        <v>15.57547053551403</v>
       </c>
       <c r="J61" t="n">
-        <v>5.761501647758126</v>
+        <v>64.20402606987432</v>
       </c>
       <c r="K61" t="n">
-        <v>16.58978730550185</v>
+        <v>1.478920045940277</v>
       </c>
     </row>
     <row r="62">
@@ -38846,25 +38846,25 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>0.9002848662126398</v>
+        <v>0.9235417287411419</v>
       </c>
       <c r="F62" t="n">
-        <v>0.7644488161871125</v>
+        <v>0.7943902831416777</v>
       </c>
       <c r="G62" t="n">
-        <v>3.759239789119267</v>
+        <v>1.490807866174425</v>
       </c>
       <c r="H62" t="n">
-        <v>4.93796172305524</v>
+        <v>2.002068621107012</v>
       </c>
       <c r="I62" t="n">
-        <v>172.1961559852246</v>
+        <v>15.30044242337567</v>
       </c>
       <c r="J62" t="n">
-        <v>5.823533820919867</v>
+        <v>65.3581820473848</v>
       </c>
       <c r="K62" t="n">
-        <v>16.26714421394004</v>
+        <v>1.445412657524682</v>
       </c>
     </row>
     <row r="63">
@@ -38889,25 +38889,25 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>0.9021413829153112</v>
+        <v>0.9307901364833598</v>
       </c>
       <c r="F63" t="n">
-        <v>0.7575501107005344</v>
+        <v>0.7837667125667425</v>
       </c>
       <c r="G63" t="n">
-        <v>3.560777518437165</v>
+        <v>0.7176594867116615</v>
       </c>
       <c r="H63" t="n">
-        <v>5.79584127122101</v>
+        <v>3.312618312228618</v>
       </c>
       <c r="I63" t="n">
-        <v>173.5216996228591</v>
+        <v>15.13188425750472</v>
       </c>
       <c r="J63" t="n">
-        <v>5.815571150601481</v>
+        <v>66.09523299919412</v>
       </c>
       <c r="K63" t="n">
-        <v>16.59582019877923</v>
+        <v>1.447231273968019</v>
       </c>
     </row>
     <row r="64">
@@ -38932,25 +38932,25 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>0.7205195768217173</v>
+        <v>0.751252205640335</v>
       </c>
       <c r="F64" t="n">
-        <v>0.5475915817275469</v>
+        <v>0.5839382459240198</v>
       </c>
       <c r="G64" t="n">
-        <v>22.97621072776555</v>
+        <v>19.86799777064885</v>
       </c>
       <c r="H64" t="n">
-        <v>31.90496106468513</v>
+        <v>27.96394748528498</v>
       </c>
       <c r="I64" t="n">
-        <v>173.1171472582857</v>
+        <v>15.32567800203643</v>
       </c>
       <c r="J64" t="n">
-        <v>5.806724358161915</v>
+        <v>65.25015887548371</v>
       </c>
       <c r="K64" t="n">
-        <v>17.21803829926858</v>
+        <v>1.524274833431854</v>
       </c>
     </row>
     <row r="65">
@@ -38975,25 +38975,25 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>0.1271027450111712</v>
+        <v>0.2184629615009358</v>
       </c>
       <c r="F65" t="n">
-        <v>0.07292086991843209</v>
+        <v>0.1272968967564321</v>
       </c>
       <c r="G65" t="n">
-        <v>86.41267307288531</v>
+        <v>76.69773960516709</v>
       </c>
       <c r="H65" t="n">
-        <v>90.93202006388174</v>
+        <v>84.29634297168512</v>
       </c>
       <c r="I65" t="n">
-        <v>174.7680069492684</v>
+        <v>15.27561033568467</v>
       </c>
       <c r="J65" t="n">
-        <v>5.730774316446671</v>
+        <v>65.46502230882056</v>
       </c>
       <c r="K65" t="n">
-        <v>17.64687303505806</v>
+        <v>1.542426218805012</v>
       </c>
     </row>
   </sheetData>
